--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/plain/mol2mol_scaffold_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/plain/mol2mol_scaffold_plain_generated_optimal.xlsx
@@ -1184,23 +1184,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:BF22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="32.7109375" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" customWidth="1"/>
-    <col min="14" max="14" width="37.7109375" customWidth="1"/>
-    <col min="15" max="15" width="38.7109375" customWidth="1"/>
-    <col min="16" max="16" width="30.7109375" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="31.7109375" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" customWidth="1"/>
+    <col min="15" max="15" width="27.7109375" customWidth="1"/>
+    <col min="16" max="16" width="26.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" customWidth="1"/>
+    <col min="18" max="19" width="22.7109375" customWidth="1"/>
+    <col min="20" max="21" width="20.7109375" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="25" width="32.7109375" customWidth="1"/>
+    <col min="26" max="26" width="28.7109375" customWidth="1"/>
+    <col min="27" max="27" width="37.7109375" customWidth="1"/>
+    <col min="28" max="28" width="38.7109375" customWidth="1"/>
+    <col min="29" max="29" width="30.7109375" customWidth="1"/>
+    <col min="30" max="31" width="13.7109375" customWidth="1"/>
+    <col min="32" max="35" width="12.7109375" customWidth="1"/>
+    <col min="36" max="36" width="21.7109375" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" customWidth="1"/>
+    <col min="39" max="39" width="15.7109375" customWidth="1"/>
+    <col min="40" max="42" width="14.7109375" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" customWidth="1"/>
+    <col min="44" max="44" width="20.7109375" customWidth="1"/>
+    <col min="45" max="45" width="13.7109375" customWidth="1"/>
+    <col min="46" max="46" width="17.7109375" customWidth="1"/>
+    <col min="47" max="48" width="12.7109375" customWidth="1"/>
+    <col min="49" max="49" width="15.7109375" customWidth="1"/>
+    <col min="50" max="50" width="18.7109375" customWidth="1"/>
+    <col min="51" max="54" width="12.7109375" customWidth="1"/>
+    <col min="55" max="55" width="18.7109375" customWidth="1"/>
+    <col min="56" max="56" width="23.7109375" customWidth="1"/>
+    <col min="57" max="57" width="25.7109375" customWidth="1"/>
+    <col min="58" max="58" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1236,55 +1265,260 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>qsar_model_count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>qsar_models_used</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>pred_logIC50_uM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pred_ic50_uM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>pred_pIC50</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_lower95</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_upper95</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_lower95</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_upper95</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_uncertainty</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>pred_cLogP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pred_logS_ESOL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_mol_per_L</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_class</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Microsome_AZ</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Hepatocyte_AZ</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Half_Life_Obach</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>PAINS_alert</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>BRENK_alert</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>NIH_alert</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>AMES</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ClinTox</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>DILI</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Carcinogens_Lagunin</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>hERG</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>CYP1A2_Veith</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C19_Veith</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C9_Veith</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2D6_Veith</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>CYP3A4_Veith</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>HIA_Hou</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Bioavailability_Ma</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>PAMPA_NCATS</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Pgp_Broccatelli</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Caco2_Wang</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>PPBR_AZ</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>VDss_Lombardo</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>molecular_weight</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>logP</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>QED</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Lipinski</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>sa_score</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>sa_accessibility</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>liability_alert_count</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>passes_qsar_uncertainty</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>passes_optimal</t>
         </is>
@@ -1311,45 +1545,170 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G2" s="3">
-        <v>0.5473052419692592</v>
-      </c>
-      <c r="H2" s="3">
-        <v>3.52618620416228</v>
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I2" s="3">
-        <v>5.452694758030741</v>
+        <v>0.5473052438641018</v>
       </c>
       <c r="J2" s="3">
+        <v>3.526186219547159</v>
+      </c>
+      <c r="K2" s="3">
+        <v>5.452694756135898</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1.308086779513351</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.5802504888132622</v>
+      </c>
+      <c r="N2" s="3">
+        <v>51.79560562003868</v>
+      </c>
+      <c r="O2" s="3">
+        <v>74.52754547638385</v>
+      </c>
+      <c r="P2" s="3">
+        <v>4.691913220486649</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.5802504888132622</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1.481821260117261</v>
+      </c>
+      <c r="S2" s="3">
+        <v>278.8545515586202</v>
+      </c>
+      <c r="T2" s="3">
+        <v>3.554622262412655</v>
+      </c>
+      <c r="U2" s="3">
+        <v>5.829204178560643</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.5802504888132622</v>
+      </c>
+      <c r="W2" s="3">
         <v>3.016700000000001</v>
       </c>
-      <c r="K2" s="3">
+      <c r="X2" s="3">
         <v>-4.882161144127976</v>
       </c>
-      <c r="L2" s="3">
+      <c r="Y2" s="3">
         <v>1.311713100101767E-05</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N2" s="3">
-        <v>23.21880149841309</v>
-      </c>
-      <c r="O2" s="3">
-        <v>26.07429122924805</v>
-      </c>
-      <c r="P2" s="3">
-        <v>42.7829475402832</v>
-      </c>
-      <c r="Q2" s="3">
+      <c r="AA2" s="3">
+        <v>23.21879959106445</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>26.07429504394531</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>42.78295135498047</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.1793070733547211</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.6316912174224854</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.6344318389892578</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.09223626554012299</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>0.9331738352775574</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>0.1351944208145142</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>0.2133276015520096</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>0.3550845980644226</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>0.3897414803504944</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>0.8482101559638977</v>
+      </c>
+      <c r="AQ2" s="3">
+        <v>0.9978948831558228</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>0.7498563528060913</v>
+      </c>
+      <c r="AS2" s="3">
+        <v>0.783575713634491</v>
+      </c>
+      <c r="AT2" s="3">
+        <v>0.7166632413864136</v>
+      </c>
+      <c r="AU2" s="3">
+        <v>-5.260924339294434</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>92.48931884765625</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>10.36054039001465</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>417.5570000000002</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>3.016700000000001</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>0.4284922319693887</v>
+      </c>
+      <c r="BA2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB2" s="3">
+        <v>3.445734396899377</v>
+      </c>
+      <c r="BC2" s="3">
+        <v>0.7282517336778469</v>
+      </c>
+      <c r="BD2" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>O=C(c1cc2c(cc1F)OCO2)N1CC2(CCN(c3cncc(C#CCCCl)c3)C2)C1</t>
+          <t>CCCCC#Cc1cncc(N2CC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1361,44 +1720,169 @@
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0.6842105263157895</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="F3" s="3">
-        <v>10.41</v>
+        <v>13.68</v>
       </c>
       <c r="G3" s="3">
-        <v>0.5576247392552036</v>
-      </c>
-      <c r="H3" s="3">
-        <v>3.610977141714381</v>
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I3" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J3" s="3">
-        <v>3.282300000000002</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K3" s="3">
-        <v>-5.250440040770092</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L3" s="3">
-        <v>5.617718319114626E-06</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+        <v>0.8822108624019729</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.2899644985417485</v>
+      </c>
+      <c r="N3" s="3">
+        <v>9.632762994425908</v>
+      </c>
+      <c r="O3" s="3">
+        <v>6.861822307180756</v>
+      </c>
+      <c r="P3" s="3">
+        <v>5.117789137598027</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.2899644985417485</v>
+      </c>
+      <c r="R3" s="3">
+        <v>2.060062730915041</v>
+      </c>
+      <c r="S3" s="3">
+        <v>28.21897790775852</v>
+      </c>
+      <c r="T3" s="3">
+        <v>4.5494587204562</v>
+      </c>
+      <c r="U3" s="3">
+        <v>5.686119554739854</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.2899644985417485</v>
+      </c>
+      <c r="W3" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="X3" s="3">
+        <v>-5.238920776532085</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>5.768716860216767E-06</v>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N3" s="3">
-        <v>62.37113189697266</v>
-      </c>
-      <c r="O3" s="3">
-        <v>55.22406768798828</v>
-      </c>
-      <c r="P3" s="3">
-        <v>42.23020935058594</v>
-      </c>
-      <c r="Q3" s="3">
+      <c r="AA3" s="3">
+        <v>62.39081573486328</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>57.58205413818359</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>51.68029022216797</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.0497056320309639</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.2396424263715744</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.8849323391914368</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.08105399459600449</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.8425236940383911</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>0.2971973717212677</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>0.7376928329467773</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>0.8714698553085327</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>0.1994397044181824</v>
+      </c>
+      <c r="AP3" s="3">
+        <v>0.9584705233573914</v>
+      </c>
+      <c r="AQ3" s="3">
+        <v>0.9998761415481567</v>
+      </c>
+      <c r="AR3" s="3">
+        <v>0.7683823108673096</v>
+      </c>
+      <c r="AS3" s="3">
+        <v>0.9477031826972961</v>
+      </c>
+      <c r="AT3" s="3">
+        <v>0.8606225848197937</v>
+      </c>
+      <c r="AU3" s="3">
+        <v>-4.662340641021729</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>99.64119720458984</v>
+      </c>
+      <c r="AW3" s="3">
+        <v>6.217146873474121</v>
+      </c>
+      <c r="AX3" s="3">
+        <v>421.4720000000002</v>
+      </c>
+      <c r="AY3" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="AZ3" s="3">
+        <v>0.5591748064230898</v>
+      </c>
+      <c r="BA3" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB3" s="3">
+        <v>3.472521984311966</v>
+      </c>
+      <c r="BC3" s="3">
+        <v>0.7252753350764483</v>
+      </c>
+      <c r="BD3" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1423,45 +1907,170 @@
         <v>6.56</v>
       </c>
       <c r="G4" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H4" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I4" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J4" s="3">
+        <v>3.610977157306949</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5.442375258869468</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.9332508602781384</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="N4" s="3">
+        <v>10.96066001159812</v>
+      </c>
+      <c r="O4" s="3">
+        <v>7.922061390836396</v>
+      </c>
+      <c r="P4" s="3">
+        <v>5.066749139721861</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2.189975866909783</v>
+      </c>
+      <c r="S4" s="3">
+        <v>33.57858503776772</v>
+      </c>
+      <c r="T4" s="3">
+        <v>4.473937608473038</v>
+      </c>
+      <c r="U4" s="3">
+        <v>5.659560670970686</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="W4" s="3">
         <v>3.453500000000002</v>
       </c>
-      <c r="K4" s="3">
+      <c r="X4" s="3">
         <v>-5.242372322098043</v>
       </c>
-      <c r="L4" s="3">
+      <c r="Y4" s="3">
         <v>5.723051814844524E-06</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N4" s="3">
+      <c r="AA4" s="3">
         <v>54.03301239013672</v>
       </c>
-      <c r="O4" s="3">
+      <c r="AB4" s="3">
         <v>51.58975982666016</v>
       </c>
-      <c r="P4" s="3">
-        <v>46.11928558349609</v>
-      </c>
-      <c r="Q4" s="3">
+      <c r="AC4" s="3">
+        <v>46.11928939819336</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.1514938771724701</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>0.3794128894805908</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.790505588054657</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.05281468108296394</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.8946078419685364</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0.4100111424922943</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0.6163969039916992</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>0.7340325713157654</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>0.2590197920799255</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>0.9837437868118286</v>
+      </c>
+      <c r="AQ4" s="3">
+        <v>0.9999759793281555</v>
+      </c>
+      <c r="AR4" s="3">
+        <v>0.7540546655654907</v>
+      </c>
+      <c r="AS4" s="3">
+        <v>0.9556649327278137</v>
+      </c>
+      <c r="AT4" s="3">
+        <v>0.8375112414360046</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>-4.578262329101562</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>98.41603851318359</v>
+      </c>
+      <c r="AW4" s="3">
+        <v>6.461911201477051</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>421.4720000000002</v>
+      </c>
+      <c r="AY4" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="AZ4" s="3">
+        <v>0.7109076812540762</v>
+      </c>
+      <c r="BA4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>3.5375694365788</v>
+      </c>
+      <c r="BC4" s="3">
+        <v>0.7180478403801334</v>
+      </c>
+      <c r="BD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([18F])c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1473,44 +2082,169 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>0.7727272727272727</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="F5" s="3">
-        <v>11.11</v>
+        <v>12.57</v>
       </c>
       <c r="G5" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H5" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I5" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J5" s="3">
-        <v>3.286700000000001</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K5" s="3">
-        <v>-5.183149985103852</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L5" s="3">
-        <v>6.559187033864989E-06</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+        <v>0.9332508602781384</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="N5" s="3">
+        <v>10.96066001159812</v>
+      </c>
+      <c r="O5" s="3">
+        <v>7.922061390836396</v>
+      </c>
+      <c r="P5" s="3">
+        <v>5.066749139721861</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2.189975866909783</v>
+      </c>
+      <c r="S5" s="3">
+        <v>33.57858503776772</v>
+      </c>
+      <c r="T5" s="3">
+        <v>4.473937608473038</v>
+      </c>
+      <c r="U5" s="3">
+        <v>5.659560670970686</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="W5" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="X5" s="3">
+        <v>-5.235777868917642</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>5.810615403983823E-06</v>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N5" s="3">
-        <v>59.47090530395508</v>
-      </c>
-      <c r="O5" s="3">
-        <v>57.21721267700195</v>
-      </c>
-      <c r="P5" s="3">
-        <v>40.80252838134766</v>
-      </c>
-      <c r="Q5" s="3">
+      <c r="AA5" s="3">
+        <v>54.02365875244141</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>51.60739898681641</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>46.01802825927734</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>0.1515597701072693</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>0.3794240057468414</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>0.7904849052429199</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>0.0527871660888195</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>0.8945648074150085</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>0.409633457660675</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>0.6159688234329224</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>0.7336847186088562</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>0.2587462067604065</v>
+      </c>
+      <c r="AP5" s="3">
+        <v>0.9837337732315063</v>
+      </c>
+      <c r="AQ5" s="3">
+        <v>0.9999759793281555</v>
+      </c>
+      <c r="AR5" s="3">
+        <v>0.7541525959968567</v>
+      </c>
+      <c r="AS5" s="3">
+        <v>0.955665111541748</v>
+      </c>
+      <c r="AT5" s="3">
+        <v>0.8373624682426453</v>
+      </c>
+      <c r="AU5" s="3">
+        <v>-4.578091621398926</v>
+      </c>
+      <c r="AV5" s="3">
+        <v>98.40773010253906</v>
+      </c>
+      <c r="AW5" s="3">
+        <v>6.452359676361084</v>
+      </c>
+      <c r="AX5" s="3">
+        <v>420.4749380000002</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>0.7122693165783467</v>
+      </c>
+      <c r="BA5" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB5" s="3">
+        <v>3.5375694365788</v>
+      </c>
+      <c r="BC5" s="3">
+        <v>0.7180478403801334</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE5" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1535,45 +2269,170 @@
         <v>12.05</v>
       </c>
       <c r="G6" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I6" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J6" s="3">
+        <v>3.610977157306949</v>
+      </c>
+      <c r="K6" s="3">
+        <v>5.442375258869468</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1.127292603598165</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.3196670958514118</v>
+      </c>
+      <c r="N6" s="3">
+        <v>16.5887214005594</v>
+      </c>
+      <c r="O6" s="3">
+        <v>8.692287910666909</v>
+      </c>
+      <c r="P6" s="3">
+        <v>4.872707396401834</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.3196670958514118</v>
+      </c>
+      <c r="R6" s="3">
+        <v>3.167707666850441</v>
+      </c>
+      <c r="S6" s="3">
+        <v>56.73356983737003</v>
+      </c>
+      <c r="T6" s="3">
+        <v>4.246159888533068</v>
+      </c>
+      <c r="U6" s="3">
+        <v>5.499254904270602</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.3196670958514118</v>
+      </c>
+      <c r="W6" s="3">
         <v>3.456900000000002</v>
       </c>
-      <c r="K6" s="3">
+      <c r="X6" s="3">
         <v>-5.390321245440994</v>
       </c>
-      <c r="L6" s="3">
+      <c r="Y6" s="3">
         <v>4.07079052085649E-06</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N6" s="3">
+      <c r="AA6" s="3">
         <v>49.53058624267578</v>
       </c>
-      <c r="O6" s="3">
+      <c r="AB6" s="3">
         <v>50.50267791748047</v>
       </c>
-      <c r="P6" s="3">
-        <v>42.52789688110352</v>
-      </c>
-      <c r="Q6" s="3">
+      <c r="AC6" s="3">
+        <v>42.52790069580078</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0.1503766477108002</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0.4014430642127991</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0.7944496870040894</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>0.06801829487085342</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0.9175645112991333</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>0.4286567568778992</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>0.7177208662033081</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0.8529923558235168</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0.3775244355201721</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>0.9936367273330688</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>0.9999710321426392</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>0.653423011302948</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>0.936070442199707</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>0.899492084980011</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>-4.60943078994751</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>99.28874969482422</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>4.949751853942871</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>445.4940000000003</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>3.456900000000002</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>0.5330893071011114</v>
+      </c>
+      <c r="BA6" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>3.712554966519908</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>0.6986050037200102</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(NC)c5c(c4)OCO5)C3)C2)c1</t>
+          <t>O=C(c1cc2c(cc1F)OCO2)N1CC2(CCN(c3cncc(C#CCCCl)c3)C2)C1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1585,44 +2444,169 @@
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>0.6115702479338843</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="F7" s="3">
-        <v>12.37</v>
+        <v>10.41</v>
       </c>
       <c r="G7" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I7" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J7" s="3">
-        <v>3.356100000000002</v>
+        <v>3.61097715730695</v>
       </c>
       <c r="K7" s="3">
-        <v>-5.234622157396311</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L7" s="3">
-        <v>5.826098765227984E-06</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+        <v>0.9042563426665993</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.2814547288330222</v>
+      </c>
+      <c r="N7" s="3">
+        <v>9.94652234047509</v>
+      </c>
+      <c r="O7" s="3">
+        <v>6.771393448582403</v>
+      </c>
+      <c r="P7" s="3">
+        <v>5.095743657333401</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.2814547288330222</v>
+      </c>
+      <c r="R7" s="3">
+        <v>2.252190250652667</v>
+      </c>
+      <c r="S7" s="3">
+        <v>28.56982703875488</v>
+      </c>
+      <c r="T7" s="3">
+        <v>4.544092388820677</v>
+      </c>
+      <c r="U7" s="3">
+        <v>5.647394925846124</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0.2814547288330222</v>
+      </c>
+      <c r="W7" s="3">
+        <v>3.282300000000002</v>
+      </c>
+      <c r="X7" s="3">
+        <v>-5.250440040770092</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>5.617718319114626E-06</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N7" s="3">
-        <v>50.03407669067383</v>
-      </c>
-      <c r="O7" s="3">
-        <v>47.67665863037109</v>
-      </c>
-      <c r="P7" s="3">
-        <v>41.62461471557617</v>
-      </c>
-      <c r="Q7" s="3">
+      <c r="AA7" s="3">
+        <v>62.37113189697266</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>55.22406768798828</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>42.23021697998047</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0.3101035356521606</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0.3923474252223969</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.8259280920028687</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0.06683068722486496</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0.89606773853302</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0.3563960790634155</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0.6407725214958191</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0.7509437799453735</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0.298628181219101</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0.9887466430664062</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>0.999965488910675</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>0.7102676630020142</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>0.9408232569694519</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>0.8539096117019653</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>-4.659994602203369</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>99.01403045654297</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>5.339962959289551</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>441.8900000000002</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>3.282300000000002</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>0.5401999713995431</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>3.543929332862292</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>0.7173411852375231</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1647,45 +2631,170 @@
         <v>12.47</v>
       </c>
       <c r="G8" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I8" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J8" s="3">
+        <v>3.61097715730695</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5.442375258869468</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1.245897807973702</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.572257881379526</v>
+      </c>
+      <c r="N8" s="3">
+        <v>48.73741213137368</v>
+      </c>
+      <c r="O8" s="3">
+        <v>75.73271444707508</v>
+      </c>
+      <c r="P8" s="3">
+        <v>4.754102192026298</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.572257881379526</v>
+      </c>
+      <c r="R8" s="3">
+        <v>1.331289051744384</v>
+      </c>
+      <c r="S8" s="3">
+        <v>233.0897926201091</v>
+      </c>
+      <c r="T8" s="3">
+        <v>3.632476744522427</v>
+      </c>
+      <c r="U8" s="3">
+        <v>5.87572763953017</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.572257881379526</v>
+      </c>
+      <c r="W8" s="3">
         <v>3.380400000000003</v>
       </c>
-      <c r="K8" s="3">
+      <c r="X8" s="3">
         <v>-5.340574064292892</v>
       </c>
-      <c r="L8" s="3">
+      <c r="Y8" s="3">
         <v>4.564843950177818E-06</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N8" s="3">
+      <c r="AA8" s="3">
         <v>67.9300537109375</v>
       </c>
-      <c r="O8" s="3">
+      <c r="AB8" s="3">
         <v>55.20512771606445</v>
       </c>
-      <c r="P8" s="3">
-        <v>40.69406509399414</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="AC8" s="3">
+        <v>40.69405746459961</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0.2426724880933762</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0.5274170637130737</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0.8195544481277466</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>0.05707133933901787</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0.9460126757621765</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0.3255794644355774</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>0.6021593809127808</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>0.7146463990211487</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0.2755510210990906</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0.9880801439285278</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>0.9999575614929199</v>
+      </c>
+      <c r="AR8" s="3">
+        <v>0.7738900184631348</v>
+      </c>
+      <c r="AS8" s="3">
+        <v>0.9560348391532898</v>
+      </c>
+      <c r="AT8" s="3">
+        <v>0.9067276120185852</v>
+      </c>
+      <c r="AU8" s="3">
+        <v>-4.787168502807617</v>
+      </c>
+      <c r="AV8" s="3">
+        <v>100.1134414672852</v>
+      </c>
+      <c r="AW8" s="3">
+        <v>7.336749076843262</v>
+      </c>
+      <c r="AX8" s="3">
+        <v>446.5510000000002</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>3.380400000000003</v>
+      </c>
+      <c r="AZ8" s="3">
+        <v>0.6714891134739217</v>
+      </c>
+      <c r="BA8" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB8" s="3">
+        <v>3.659550990294565</v>
+      </c>
+      <c r="BC8" s="3">
+        <v>0.7044943344117149</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="92" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([18F])c5c(c4)OCO5)C3)C2)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(NC)c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1697,51 +2806,176 @@
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>0.6271186440677966</v>
+        <v>0.6115702479338843</v>
       </c>
       <c r="F9" s="3">
-        <v>12.57</v>
+        <v>12.37</v>
       </c>
       <c r="G9" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I9" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J9" s="3">
-        <v>3.453500000000002</v>
+        <v>3.61097715730695</v>
       </c>
       <c r="K9" s="3">
-        <v>-5.235777868917642</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L9" s="3">
-        <v>5.810615403983823E-06</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+        <v>1.238444555986427</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.5761692979434486</v>
+      </c>
+      <c r="N9" s="3">
+        <v>48.60572225291012</v>
+      </c>
+      <c r="O9" s="3">
+        <v>75.81157343115541</v>
+      </c>
+      <c r="P9" s="3">
+        <v>4.761555444013574</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.5761692979434486</v>
+      </c>
+      <c r="R9" s="3">
+        <v>1.285738747074785</v>
+      </c>
+      <c r="S9" s="3">
+        <v>233.2042065343045</v>
+      </c>
+      <c r="T9" s="3">
+        <v>3.632263620044414</v>
+      </c>
+      <c r="U9" s="3">
+        <v>5.890847267982733</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0.5761692979434486</v>
+      </c>
+      <c r="W9" s="3">
+        <v>3.356100000000002</v>
+      </c>
+      <c r="X9" s="3">
+        <v>-5.234622157396311</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>5.826098765227984E-06</v>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N9" s="3">
-        <v>54.02365875244141</v>
-      </c>
-      <c r="O9" s="3">
-        <v>51.60739898681641</v>
-      </c>
-      <c r="P9" s="3">
-        <v>46.01802825927734</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="AA9" s="3">
+        <v>50.03407287597656</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>47.67665863037109</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>41.62461090087891</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0.2527405917644501</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0.4688826203346252</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0.8351690173149109</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>0.04883065074682236</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>0.9386070370674133</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>0.3703396916389465</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>0.6521976590156555</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>0.7791668176651001</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>0.2660719156265259</v>
+      </c>
+      <c r="AP9" s="3">
+        <v>0.9907934069633484</v>
+      </c>
+      <c r="AQ9" s="3">
+        <v>0.9999765157699585</v>
+      </c>
+      <c r="AR9" s="3">
+        <v>0.7638531923294067</v>
+      </c>
+      <c r="AS9" s="3">
+        <v>0.9541949033737183</v>
+      </c>
+      <c r="AT9" s="3">
+        <v>0.8792737722396851</v>
+      </c>
+      <c r="AU9" s="3">
+        <v>-4.85697603225708</v>
+      </c>
+      <c r="AV9" s="3">
+        <v>99.01522064208984</v>
+      </c>
+      <c r="AW9" s="3">
+        <v>8.199435234069824</v>
+      </c>
+      <c r="AX9" s="3">
+        <v>432.5240000000002</v>
+      </c>
+      <c r="AY9" s="3">
+        <v>3.356100000000002</v>
+      </c>
+      <c r="AZ9" s="3">
+        <v>0.7477497026220111</v>
+      </c>
+      <c r="BA9" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB9" s="3">
+        <v>3.593258458800245</v>
+      </c>
+      <c r="BC9" s="3">
+        <v>0.7118601712444173</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="92" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1753,44 +2987,169 @@
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>0.5916666666666667</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="F10" s="3">
-        <v>13.68</v>
+        <v>11.11</v>
       </c>
       <c r="G10" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I10" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J10" s="3">
-        <v>3.453500000000002</v>
+        <v>3.61097715730695</v>
       </c>
       <c r="K10" s="3">
-        <v>-5.238920776532085</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L10" s="3">
-        <v>5.768716860216767E-06</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+        <v>1.202643999226805</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="N10" s="3">
+        <v>48.16748725694215</v>
+      </c>
+      <c r="O10" s="3">
+        <v>76.0808612751983</v>
+      </c>
+      <c r="P10" s="3">
+        <v>4.797356000773195</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1.049982151963999</v>
+      </c>
+      <c r="S10" s="3">
+        <v>242.1620484371657</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3.61589391835973</v>
+      </c>
+      <c r="U10" s="3">
+        <v>5.97881808318666</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="W10" s="3">
+        <v>3.286700000000001</v>
+      </c>
+      <c r="X10" s="3">
+        <v>-5.183149985103852</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>6.559187033864989E-06</v>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N10" s="3">
-        <v>62.39081573486328</v>
-      </c>
-      <c r="O10" s="3">
-        <v>57.58205413818359</v>
-      </c>
-      <c r="P10" s="3">
-        <v>51.68029022216797</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="AA10" s="3">
+        <v>59.47090530395508</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>57.21721267700195</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>40.80252838134766</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.1844686716794968</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0.4202435612678528</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0.8358316421508789</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>0.04515016824007034</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0.9386307597160339</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0.4181106984615326</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>0.7442826628684998</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>0.8617993593215942</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0.2975649237632751</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>0.9936869740486145</v>
+      </c>
+      <c r="AQ10" s="3">
+        <v>0.9999872446060181</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>0.721790075302124</v>
+      </c>
+      <c r="AS10" s="3">
+        <v>0.957022488117218</v>
+      </c>
+      <c r="AT10" s="3">
+        <v>0.9055355191230774</v>
+      </c>
+      <c r="AU10" s="3">
+        <v>-4.767285823822021</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>101.1879043579102</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>5.74851131439209</v>
+      </c>
+      <c r="AX10" s="3">
+        <v>432.5240000000002</v>
+      </c>
+      <c r="AY10" s="3">
+        <v>3.286700000000001</v>
+      </c>
+      <c r="AZ10" s="3">
+        <v>0.4537042148229764</v>
+      </c>
+      <c r="BA10" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB10" s="3">
+        <v>3.481991067495898</v>
+      </c>
+      <c r="BC10" s="3">
+        <v>0.724223214722678</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1815,38 +3174,163 @@
         <v>11.94</v>
       </c>
       <c r="G11" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H11" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I11" s="3">
-        <v>5.394846104919416</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J11" s="3">
+        <v>4.028597666980577</v>
+      </c>
+      <c r="K11" s="3">
+        <v>5.394846103109279</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1.062807256274008</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.3276109864609245</v>
+      </c>
+      <c r="N11" s="3">
+        <v>14.9370461103721</v>
+      </c>
+      <c r="O11" s="3">
+        <v>9.749179286565441</v>
+      </c>
+      <c r="P11" s="3">
+        <v>4.937192743725992</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.3276109864609245</v>
+      </c>
+      <c r="R11" s="3">
+        <v>2.634448558866033</v>
+      </c>
+      <c r="S11" s="3">
+        <v>50.69029162249384</v>
+      </c>
+      <c r="T11" s="3">
+        <v>4.29507521026258</v>
+      </c>
+      <c r="U11" s="3">
+        <v>5.579310277189404</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.3276109864609245</v>
+      </c>
+      <c r="W11" s="3">
         <v>3.442100000000003</v>
       </c>
-      <c r="K11" s="3">
+      <c r="X11" s="3">
         <v>-5.169985558383089</v>
       </c>
-      <c r="L11" s="3">
+      <c r="Y11" s="3">
         <v>6.761054575879949E-06</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N11" s="3">
+      <c r="AA11" s="3">
         <v>12.38687324523926</v>
       </c>
-      <c r="O11" s="3">
+      <c r="AB11" s="3">
         <v>28.63481521606445</v>
       </c>
-      <c r="P11" s="3">
+      <c r="AC11" s="3">
         <v>41.37298583984375</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.1577767580747604</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0.5154687762260437</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0.3734657168388367</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>0.09895943105220795</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>0.9235855340957642</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>0.0505656786262989</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>0.1717598289251328</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>0.1719331741333008</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0.4868618547916412</v>
+      </c>
+      <c r="AP11" s="3">
+        <v>0.6581208109855652</v>
+      </c>
+      <c r="AQ11" s="3">
+        <v>0.9986150860786438</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>0.7258269190788269</v>
+      </c>
+      <c r="AS11" s="3">
+        <v>0.8411421775817871</v>
+      </c>
+      <c r="AT11" s="3">
+        <v>0.7036873698234558</v>
+      </c>
+      <c r="AU11" s="3">
+        <v>-4.742566585540771</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>86.36440277099609</v>
+      </c>
+      <c r="AW11" s="3">
+        <v>11.66602993011475</v>
+      </c>
+      <c r="AX11" s="3">
+        <v>411.4960000000001</v>
+      </c>
+      <c r="AY11" s="3">
+        <v>3.442100000000003</v>
+      </c>
+      <c r="AZ11" s="3">
+        <v>0.7827965706123682</v>
+      </c>
+      <c r="BA11" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="3">
+        <v>3.624855675086121</v>
+      </c>
+      <c r="BC11" s="3">
+        <v>0.7083493694348755</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1871,45 +3355,170 @@
         <v>10.69</v>
       </c>
       <c r="G12" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H12" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I12" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J12" s="3">
+        <v>4.028597666980578</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5.394846103109279</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1.350083032418545</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="N12" s="3">
+        <v>52.85744973393292</v>
+      </c>
+      <c r="O12" s="3">
+        <v>73.97049186169482</v>
+      </c>
+      <c r="P12" s="3">
+        <v>4.649916967581455</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.838418337923174</v>
+      </c>
+      <c r="S12" s="3">
+        <v>272.7229723024533</v>
+      </c>
+      <c r="T12" s="3">
+        <v>3.564278278545373</v>
+      </c>
+      <c r="U12" s="3">
+        <v>5.735555656617537</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="W12" s="3">
         <v>3.233900000000002</v>
       </c>
-      <c r="K12" s="3">
+      <c r="X12" s="3">
         <v>-5.050155817708335</v>
       </c>
-      <c r="L12" s="3">
+      <c r="Y12" s="3">
         <v>8.909312293304308E-06</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N12" s="3">
+      <c r="AA12" s="3">
         <v>39.75581741333008</v>
       </c>
-      <c r="O12" s="3">
+      <c r="AB12" s="3">
         <v>32.81678771972656</v>
       </c>
-      <c r="P12" s="3">
-        <v>42.63827133178711</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="AC12" s="3">
+        <v>42.63826751708984</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0.3349597156047821</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0.4971658289432526</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>0.8305774927139282</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>0.05206187814474106</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>0.9213894605636597</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>0.2205078601837158</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>0.4619075655937195</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>0.5620790719985962</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0.1509415358304977</v>
+      </c>
+      <c r="AP12" s="3">
+        <v>0.957487940788269</v>
+      </c>
+      <c r="AQ12" s="3">
+        <v>0.9998504519462585</v>
+      </c>
+      <c r="AR12" s="3">
+        <v>0.8074136972427368</v>
+      </c>
+      <c r="AS12" s="3">
+        <v>0.9490911364555359</v>
+      </c>
+      <c r="AT12" s="3">
+        <v>0.8077398538589478</v>
+      </c>
+      <c r="AU12" s="3">
+        <v>-4.965895175933838</v>
+      </c>
+      <c r="AV12" s="3">
+        <v>95.56562805175781</v>
+      </c>
+      <c r="AW12" s="3">
+        <v>10.71188068389893</v>
+      </c>
+      <c r="AX12" s="3">
+        <v>417.5570000000001</v>
+      </c>
+      <c r="AY12" s="3">
+        <v>3.233900000000002</v>
+      </c>
+      <c r="AZ12" s="3">
+        <v>0.6111796571419246</v>
+      </c>
+      <c r="BA12" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB12" s="3">
+        <v>3.50520040847401</v>
+      </c>
+      <c r="BC12" s="3">
+        <v>0.7216443990584434</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="92" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)cc(F)c4)C3)C2)c1</t>
+          <t>CCOCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)cc(F)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1921,156 +3530,531 @@
         <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>0.5258620689655172</v>
+        <v>0.55</v>
       </c>
       <c r="F13" s="3">
-        <v>9.789999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="G13" s="3">
-        <v>0.6269673212607438</v>
-      </c>
-      <c r="H13" s="3">
-        <v>4.236110899890319</v>
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I13" s="3">
-        <v>5.373032678739256</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J13" s="3">
-        <v>3.083700000000001</v>
+        <v>4.236110917115642</v>
       </c>
       <c r="K13" s="3">
-        <v>-4.638364601652299</v>
+        <v>5.373032676973282</v>
       </c>
       <c r="L13" s="3">
-        <v>2.299510507213377E-05</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+        <v>0.9694351944564714</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.2834425266854452</v>
+      </c>
+      <c r="N13" s="3">
+        <v>11.70816753590797</v>
+      </c>
+      <c r="O13" s="3">
+        <v>8.521556365489404</v>
+      </c>
+      <c r="P13" s="3">
+        <v>5.030564805543529</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.2834425266854452</v>
+      </c>
+      <c r="R13" s="3">
+        <v>2.593509494052293</v>
+      </c>
+      <c r="S13" s="3">
+        <v>33.49519779811553</v>
+      </c>
+      <c r="T13" s="3">
+        <v>4.475017453240056</v>
+      </c>
+      <c r="U13" s="3">
+        <v>5.586112157847001</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.2834425266854452</v>
+      </c>
+      <c r="W13" s="3">
+        <v>3.100300000000002</v>
+      </c>
+      <c r="X13" s="3">
+        <v>-4.916190390542918</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1.212857028991192E-05</v>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N13" s="3">
-        <v>44.03082275390625</v>
-      </c>
-      <c r="O13" s="3">
-        <v>52.28588104248047</v>
-      </c>
-      <c r="P13" s="3">
-        <v>46.47860336303711</v>
-      </c>
-      <c r="Q13" s="3">
+      <c r="AA13" s="3">
+        <v>38.1949577331543</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>46.53000640869141</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>52.06615447998047</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.14383664727211</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0.2526366710662842</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.7948338389396667</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0.05038211867213249</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0.7190860509872437</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0.1829346120357513</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0.3825122117996216</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0.4498942494392395</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0.06359347701072693</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0.8871018290519714</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0.9999326467514038</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>0.8340275883674622</v>
+      </c>
+      <c r="AS13" s="3">
+        <v>0.9630118608474731</v>
+      </c>
+      <c r="AT13" s="3">
+        <v>0.621238112449646</v>
+      </c>
+      <c r="AU13" s="3">
+        <v>-4.4007568359375</v>
+      </c>
+      <c r="AV13" s="3">
+        <v>87.47709655761719</v>
+      </c>
+      <c r="AW13" s="3">
+        <v>9.734238624572754</v>
+      </c>
+      <c r="AX13" s="3">
+        <v>411.4520000000001</v>
+      </c>
+      <c r="AY13" s="3">
+        <v>3.100300000000002</v>
+      </c>
+      <c r="AZ13" s="3">
+        <v>0.5730741551139058</v>
+      </c>
+      <c r="BA13" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="3">
+        <v>3.425429773340808</v>
+      </c>
+      <c r="BC13" s="3">
+        <v>0.7305078029621325</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="92" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
+          <t>CC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)cc(F)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>0.5882352941176471</v>
+        <v>0.5258620689655172</v>
       </c>
       <c r="F14" s="3">
-        <v>13.93</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G14" s="3">
-        <v>0.6269673212607438</v>
-      </c>
-      <c r="H14" s="3">
-        <v>4.236110899890319</v>
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I14" s="3">
-        <v>5.373032678739256</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J14" s="3">
-        <v>3.063400000000001</v>
+        <v>4.236110917115642</v>
       </c>
       <c r="K14" s="3">
-        <v>-4.869223876544572</v>
+        <v>5.373032676973282</v>
       </c>
       <c r="L14" s="3">
-        <v>1.351375756442124E-05</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+        <v>0.9412992172191981</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.3091094834936228</v>
+      </c>
+      <c r="N14" s="3">
+        <v>11.8801137238013</v>
+      </c>
+      <c r="O14" s="3">
+        <v>10.99309258584417</v>
+      </c>
+      <c r="P14" s="3">
+        <v>5.058700782780802</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.3091094834936228</v>
+      </c>
+      <c r="R14" s="3">
+        <v>2.164933843205475</v>
+      </c>
+      <c r="S14" s="3">
+        <v>35.24956848612847</v>
+      </c>
+      <c r="T14" s="3">
+        <v>4.452846195133301</v>
+      </c>
+      <c r="U14" s="3">
+        <v>5.664555370428303</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.3091094834936228</v>
+      </c>
+      <c r="W14" s="3">
+        <v>3.083700000000001</v>
+      </c>
+      <c r="X14" s="3">
+        <v>-4.638364601652299</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>2.299510507213377E-05</v>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N14" s="3">
-        <v>46.68682098388672</v>
-      </c>
-      <c r="O14" s="3">
-        <v>46.50349807739258</v>
-      </c>
-      <c r="P14" s="3">
-        <v>40.06744384765625</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="AA14" s="3">
+        <v>44.03082275390625</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>52.285888671875</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>46.47860336303711</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.1481298804283142</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.2408362925052643</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0.7796632647514343</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0.04402393475174904</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0.6242526769638062</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0.1550628244876862</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0.2458717375993729</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0.2648356854915619</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0.03013483621180058</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0.7748692631721497</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0.9999569058418274</v>
+      </c>
+      <c r="AR14" s="3">
+        <v>0.8821442723274231</v>
+      </c>
+      <c r="AS14" s="3">
+        <v>0.9609131813049316</v>
+      </c>
+      <c r="AT14" s="3">
+        <v>0.4224107265472412</v>
+      </c>
+      <c r="AU14" s="3">
+        <v>-4.425469398498535</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>90.94108581542969</v>
+      </c>
+      <c r="AW14" s="3">
+        <v>7.25708532333374</v>
+      </c>
+      <c r="AX14" s="3">
+        <v>367.3990000000001</v>
+      </c>
+      <c r="AY14" s="3">
+        <v>3.083700000000001</v>
+      </c>
+      <c r="AZ14" s="3">
+        <v>0.7657274742946089</v>
+      </c>
+      <c r="BA14" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB14" s="3">
+        <v>3.350980652190577</v>
+      </c>
+      <c r="BC14" s="3">
+        <v>0.7387799275343803</v>
+      </c>
+      <c r="BD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="92" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CCOCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)cc(F)c4)C3)C2)c1</t>
+          <t>CCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D15" s="3">
         <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>0.55</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F15" s="3">
-        <v>11.02</v>
+        <v>13.93</v>
       </c>
       <c r="G15" s="3">
-        <v>0.6269673212607439</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4.23611089989032</v>
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I15" s="3">
-        <v>5.373032678739256</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J15" s="3">
-        <v>3.100300000000002</v>
+        <v>4.236110917115642</v>
       </c>
       <c r="K15" s="3">
-        <v>-4.916190390542918</v>
+        <v>5.373032676973282</v>
       </c>
       <c r="L15" s="3">
-        <v>1.212857028991192E-05</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+        <v>0.9143198987014124</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="N15" s="3">
+        <v>11.01512230952236</v>
+      </c>
+      <c r="O15" s="3">
+        <v>9.218476447745267</v>
+      </c>
+      <c r="P15" s="3">
+        <v>5.085680101298587</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.971631550060213</v>
+      </c>
+      <c r="S15" s="3">
+        <v>34.18330407657724</v>
+      </c>
+      <c r="T15" s="3">
+        <v>4.466185961718441</v>
+      </c>
+      <c r="U15" s="3">
+        <v>5.705174240878733</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="W15" s="3">
+        <v>3.063400000000001</v>
+      </c>
+      <c r="X15" s="3">
+        <v>-4.869223876544572</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>1.351375756442124E-05</v>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N15" s="3">
-        <v>38.19495391845703</v>
-      </c>
-      <c r="O15" s="3">
-        <v>46.53000640869141</v>
-      </c>
-      <c r="P15" s="3">
-        <v>52.06615447998047</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="AA15" s="3">
+        <v>46.68682098388672</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>46.50349807739258</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>40.06744003295898</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0.1574867814779282</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0.357526034116745</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0.7977760434150696</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0.05292393639683723</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0.86536705493927</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0.3862963616847992</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0.5458816289901733</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0.6691521406173706</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0.2068126946687698</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0.9757219552993774</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0.9999698400497437</v>
+      </c>
+      <c r="AR15" s="3">
+        <v>0.7815946936607361</v>
+      </c>
+      <c r="AS15" s="3">
+        <v>0.9552289843559265</v>
+      </c>
+      <c r="AT15" s="3">
+        <v>0.7651858329772949</v>
+      </c>
+      <c r="AU15" s="3">
+        <v>-4.575211524963379</v>
+      </c>
+      <c r="AV15" s="3">
+        <v>96.03324890136719</v>
+      </c>
+      <c r="AW15" s="3">
+        <v>5.789505958557129</v>
+      </c>
+      <c r="AX15" s="3">
+        <v>407.4450000000002</v>
+      </c>
+      <c r="AY15" s="3">
+        <v>3.063400000000001</v>
+      </c>
+      <c r="AZ15" s="3">
+        <v>0.7165847331452173</v>
+      </c>
+      <c r="BA15" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB15" s="3">
+        <v>3.54380626287043</v>
+      </c>
+      <c r="BC15" s="3">
+        <v>0.7173548596810633</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2095,157 +4079,532 @@
         <v>11.41</v>
       </c>
       <c r="G16" s="3">
-        <v>0.6469113461048441</v>
-      </c>
-      <c r="H16" s="3">
-        <v>4.435180979491915</v>
+        <v>5</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I16" s="3">
-        <v>5.353088653895156</v>
+        <v>0.6469113478524566</v>
       </c>
       <c r="J16" s="3">
+        <v>4.435180997339201</v>
+      </c>
+      <c r="K16" s="3">
+        <v>5.353088652147544</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.938415746718696</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.2372612585811648</v>
+      </c>
+      <c r="N16" s="3">
+        <v>9.948615853378566</v>
+      </c>
+      <c r="O16" s="3">
+        <v>4.720486377716839</v>
+      </c>
+      <c r="P16" s="3">
+        <v>5.061584253281304</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.2372612585811648</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2.974292526811678</v>
+      </c>
+      <c r="S16" s="3">
+        <v>25.31907373465372</v>
+      </c>
+      <c r="T16" s="3">
+        <v>4.596552186462221</v>
+      </c>
+      <c r="U16" s="3">
+        <v>5.526616320100387</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0.2372612585811648</v>
+      </c>
+      <c r="W16" s="3">
         <v>3.314000000000002</v>
       </c>
-      <c r="K16" s="3">
+      <c r="X16" s="3">
         <v>-5.017454811696665</v>
       </c>
-      <c r="L16" s="3">
+      <c r="Y16" s="3">
         <v>9.606057641337639E-06</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N16" s="3">
+      <c r="AA16" s="3">
         <v>32.87833404541016</v>
       </c>
-      <c r="O16" s="3">
+      <c r="AB16" s="3">
         <v>23.18183326721191</v>
       </c>
-      <c r="P16" s="3">
-        <v>52.36696243286133</v>
-      </c>
-      <c r="Q16" s="3">
+      <c r="AC16" s="3">
+        <v>52.3669548034668</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>0.1258585155010223</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>0.2497570961713791</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0.8550773859024048</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>0.06400169432163239</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>0.6612062454223633</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>0.2865390479564667</v>
+      </c>
+      <c r="AM16" s="3">
+        <v>0.342566967010498</v>
+      </c>
+      <c r="AN16" s="3">
+        <v>0.4608745574951172</v>
+      </c>
+      <c r="AO16" s="3">
+        <v>0.05450470373034477</v>
+      </c>
+      <c r="AP16" s="3">
+        <v>0.763884425163269</v>
+      </c>
+      <c r="AQ16" s="3">
+        <v>0.9998586773872375</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>0.8826817274093628</v>
+      </c>
+      <c r="AS16" s="3">
+        <v>0.9536167979240417</v>
+      </c>
+      <c r="AT16" s="3">
+        <v>0.5413268208503723</v>
+      </c>
+      <c r="AU16" s="3">
+        <v>-4.699678897857666</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>97.27809143066406</v>
+      </c>
+      <c r="AW16" s="3">
+        <v>4.346566200256348</v>
+      </c>
+      <c r="AX16" s="3">
+        <v>401.3880000000001</v>
+      </c>
+      <c r="AY16" s="3">
+        <v>3.314000000000002</v>
+      </c>
+      <c r="AZ16" s="3">
+        <v>0.7407372625555321</v>
+      </c>
+      <c r="BA16" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB16" s="3">
+        <v>3.294079103551696</v>
+      </c>
+      <c r="BC16" s="3">
+        <v>0.7451023218275894</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="92" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CCOCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(C(F)(F)F)c4)C3)C2)c1</t>
+          <t>Nc1c(C(=O)N2CCC3(C2)CN(c2cncc(C#CCCC(F)(F)F)c2)C3)ccc2c1OCO2</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="3">
-        <v>0.5196850393700787</v>
+        <v>0.5190839694656488</v>
       </c>
       <c r="F17" s="3">
-        <v>11.14</v>
+        <v>13.72</v>
       </c>
       <c r="G17" s="3">
-        <v>0.685658451525513</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4.849069977611022</v>
+        <v>5</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I17" s="3">
-        <v>5.314341548474487</v>
+        <v>0.6856584533117636</v>
       </c>
       <c r="J17" s="3">
-        <v>3.423100000000002</v>
+        <v>4.849069997555217</v>
       </c>
       <c r="K17" s="3">
-        <v>-5.4511670290644</v>
+        <v>5.314341546688237</v>
       </c>
       <c r="L17" s="3">
-        <v>3.538612203672896E-06</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
+        <v>1.150017631584046</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.3374879848150368</v>
+      </c>
+      <c r="N17" s="3">
+        <v>18.29353909935588</v>
+      </c>
+      <c r="O17" s="3">
+        <v>11.11256893950765</v>
+      </c>
+      <c r="P17" s="3">
+        <v>4.849982368415954</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.3374879848150368</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.079932377792606</v>
+      </c>
+      <c r="S17" s="3">
+        <v>64.7879266486885</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4.188505918178482</v>
+      </c>
+      <c r="U17" s="3">
+        <v>5.511458818653426</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.3374879848150368</v>
+      </c>
+      <c r="W17" s="3">
+        <v>3.439000000000003</v>
+      </c>
+      <c r="X17" s="3">
+        <v>-5.554334334801244</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>2.790394872403081E-06</v>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N17" s="3">
-        <v>17.60326766967773</v>
-      </c>
-      <c r="O17" s="3">
-        <v>15.00508594512939</v>
-      </c>
-      <c r="P17" s="3">
-        <v>60.34128570556641</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="AA17" s="3">
+        <v>27.08931350708008</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>20.42182159423828</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>50.60114288330078</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0.1081468015909195</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0.3498961627483368</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0.8508683443069458</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>0.04858251661062241</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>0.8946163058280945</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>0.277321994304657</v>
+      </c>
+      <c r="AM17" s="3">
+        <v>0.6814661026000977</v>
+      </c>
+      <c r="AN17" s="3">
+        <v>0.8180168867111206</v>
+      </c>
+      <c r="AO17" s="3">
+        <v>0.2221898287534714</v>
+      </c>
+      <c r="AP17" s="3">
+        <v>0.9871047139167786</v>
+      </c>
+      <c r="AQ17" s="3">
+        <v>0.9999736547470093</v>
+      </c>
+      <c r="AR17" s="3">
+        <v>0.761349618434906</v>
+      </c>
+      <c r="AS17" s="3">
+        <v>0.9597161412239075</v>
+      </c>
+      <c r="AT17" s="3">
+        <v>0.8450393676757812</v>
+      </c>
+      <c r="AU17" s="3">
+        <v>-4.713494300842285</v>
+      </c>
+      <c r="AV17" s="3">
+        <v>97.13545227050781</v>
+      </c>
+      <c r="AW17" s="3">
+        <v>5.66744327545166</v>
+      </c>
+      <c r="AX17" s="3">
+        <v>472.4670000000003</v>
+      </c>
+      <c r="AY17" s="3">
+        <v>3.439000000000003</v>
+      </c>
+      <c r="AZ17" s="3">
+        <v>0.5447127640098829</v>
+      </c>
+      <c r="BA17" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB17" s="3">
+        <v>3.761500990265453</v>
+      </c>
+      <c r="BC17" s="3">
+        <v>0.6931665566371719</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="92" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Nc1c(C(=O)N2CCC3(C2)CN(c2cncc(C#CCCC(F)(F)F)c2)C3)ccc2c1OCO2</t>
+          <t>CCOCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(C(F)(F)F)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="3">
-        <v>0.5190839694656488</v>
+        <v>0.5196850393700787</v>
       </c>
       <c r="F18" s="3">
-        <v>13.72</v>
+        <v>11.14</v>
       </c>
       <c r="G18" s="3">
-        <v>0.685658451525513</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4.849069977611022</v>
+        <v>5</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I18" s="3">
-        <v>5.314341548474487</v>
+        <v>0.6856584533117636</v>
       </c>
       <c r="J18" s="3">
-        <v>3.439000000000003</v>
+        <v>4.849069997555217</v>
       </c>
       <c r="K18" s="3">
-        <v>-5.554334334801244</v>
+        <v>5.314341546688237</v>
       </c>
       <c r="L18" s="3">
-        <v>2.790394872403081E-06</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
+        <v>1.328082609157196</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.53055000799915</v>
+      </c>
+      <c r="N18" s="3">
+        <v>50.98123533863175</v>
+      </c>
+      <c r="O18" s="3">
+        <v>74.67271833654489</v>
+      </c>
+      <c r="P18" s="3">
+        <v>4.671917390842804</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.53055000799915</v>
+      </c>
+      <c r="R18" s="3">
+        <v>1.941800432483435</v>
+      </c>
+      <c r="S18" s="3">
+        <v>233.3246509673746</v>
+      </c>
+      <c r="T18" s="3">
+        <v>3.63203937516447</v>
+      </c>
+      <c r="U18" s="3">
+        <v>5.711795406521137</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0.53055000799915</v>
+      </c>
+      <c r="W18" s="3">
+        <v>3.423100000000002</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-5.4511670290644</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>3.538612203672896E-06</v>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N18" s="3">
-        <v>27.08931350708008</v>
-      </c>
-      <c r="O18" s="3">
-        <v>20.42182159423828</v>
-      </c>
-      <c r="P18" s="3">
-        <v>50.60114288330078</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="AA18" s="3">
+        <v>17.603271484375</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>15.00508689880371</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>60.3412971496582</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0.1759376376867294</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0.3225483298301697</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0.8475942611694336</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>0.0409967452287674</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>0.850246250629425</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>0.1296553909778595</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>0.3709774911403656</v>
+      </c>
+      <c r="AN18" s="3">
+        <v>0.5289421081542969</v>
+      </c>
+      <c r="AO18" s="3">
+        <v>0.06528114527463913</v>
+      </c>
+      <c r="AP18" s="3">
+        <v>0.9636019468307495</v>
+      </c>
+      <c r="AQ18" s="3">
+        <v>0.999913215637207</v>
+      </c>
+      <c r="AR18" s="3">
+        <v>0.8498846292495728</v>
+      </c>
+      <c r="AS18" s="3">
+        <v>0.9663764238357544</v>
+      </c>
+      <c r="AT18" s="3">
+        <v>0.7521975040435791</v>
+      </c>
+      <c r="AU18" s="3">
+        <v>-4.828359127044678</v>
+      </c>
+      <c r="AV18" s="3">
+        <v>92.74420928955078</v>
+      </c>
+      <c r="AW18" s="3">
+        <v>11.26456642150879</v>
+      </c>
+      <c r="AX18" s="3">
+        <v>458.4840000000002</v>
+      </c>
+      <c r="AY18" s="3">
+        <v>3.423100000000002</v>
+      </c>
+      <c r="AZ18" s="3">
+        <v>0.4319787741095225</v>
+      </c>
+      <c r="BA18" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB18" s="3">
+        <v>3.569114183207111</v>
+      </c>
+      <c r="BC18" s="3">
+        <v>0.7145428685325432</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="92" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN(Cc4cc(NC)cc(C(N)=O)c4)C3)C2)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(Cc4cc(F)cc(C(=O)NC)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2257,44 +4616,169 @@
         <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>0.6101694915254238</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F19" s="3">
-        <v>10.74</v>
+        <v>10.37</v>
       </c>
       <c r="G19" s="3">
-        <v>0.6976196057554537</v>
-      </c>
-      <c r="H19" s="3">
-        <v>4.984477107800574</v>
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I19" s="3">
-        <v>5.302380394244547</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J19" s="3">
-        <v>3.476200000000001</v>
+        <v>4.984477127902903</v>
       </c>
       <c r="K19" s="3">
-        <v>-5.307125510687144</v>
+        <v>5.302380392493043</v>
       </c>
       <c r="L19" s="3">
-        <v>4.930312977934696E-06</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
+        <v>0.9517987084885606</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.3029378978846305</v>
+      </c>
+      <c r="N19" s="3">
+        <v>12.12319990519978</v>
+      </c>
+      <c r="O19" s="3">
+        <v>11.30303816696889</v>
+      </c>
+      <c r="P19" s="3">
+        <v>5.04820129151144</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.3029378978846305</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2.280554359771994</v>
+      </c>
+      <c r="S19" s="3">
+        <v>35.12020063983896</v>
+      </c>
+      <c r="T19" s="3">
+        <v>4.454443011657563</v>
+      </c>
+      <c r="U19" s="3">
+        <v>5.641959571365315</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0.3029378978846305</v>
+      </c>
+      <c r="W19" s="3">
+        <v>3.444200000000002</v>
+      </c>
+      <c r="X19" s="3">
+        <v>-5.222354611521923</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>5.993015328130731E-06</v>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N19" s="3">
-        <v>31.98368453979492</v>
-      </c>
-      <c r="O19" s="3">
-        <v>31.56573486328125</v>
-      </c>
-      <c r="P19" s="3">
-        <v>51.06867218017578</v>
-      </c>
-      <c r="Q19" s="3">
+      <c r="AA19" s="3">
+        <v>24.07105827331543</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>23.20031547546387</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>48.26595687866211</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>0.1182065233588219</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>0.6393347382545471</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0.604170024394989</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>0.1051495298743248</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>0.9317499995231628</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>0.1908909529447556</v>
+      </c>
+      <c r="AM19" s="3">
+        <v>0.2398413419723511</v>
+      </c>
+      <c r="AN19" s="3">
+        <v>0.3507117331027985</v>
+      </c>
+      <c r="AO19" s="3">
+        <v>0.4600063264369965</v>
+      </c>
+      <c r="AP19" s="3">
+        <v>0.8681474924087524</v>
+      </c>
+      <c r="AQ19" s="3">
+        <v>0.9994595646858215</v>
+      </c>
+      <c r="AR19" s="3">
+        <v>0.7938547134399414</v>
+      </c>
+      <c r="AS19" s="3">
+        <v>0.8756176233291626</v>
+      </c>
+      <c r="AT19" s="3">
+        <v>0.7619529962539673</v>
+      </c>
+      <c r="AU19" s="3">
+        <v>-4.984997749328613</v>
+      </c>
+      <c r="AV19" s="3">
+        <v>94.06256103515625</v>
+      </c>
+      <c r="AW19" s="3">
+        <v>10.70411396026611</v>
+      </c>
+      <c r="AX19" s="3">
+        <v>420.5320000000001</v>
+      </c>
+      <c r="AY19" s="3">
+        <v>3.444200000000002</v>
+      </c>
+      <c r="AZ19" s="3">
+        <v>0.7531597574136744</v>
+      </c>
+      <c r="BA19" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="3">
+        <v>3.399046110186091</v>
+      </c>
+      <c r="BC19" s="3">
+        <v>0.7334393210904344</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE19" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2319,38 +4803,163 @@
         <v>11.14</v>
       </c>
       <c r="G20" s="3">
-        <v>0.6976196057554537</v>
-      </c>
-      <c r="H20" s="3">
-        <v>4.984477107800574</v>
+        <v>5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I20" s="3">
-        <v>5.302380394244547</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J20" s="3">
+        <v>4.984477127902903</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5.302380392493043</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1.323381249166445</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.5290540528382506</v>
+      </c>
+      <c r="N20" s="3">
+        <v>50.73423555056294</v>
+      </c>
+      <c r="O20" s="3">
+        <v>74.7807011777699</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4.676618750833556</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0.5290540528382506</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1.933905754141652</v>
+      </c>
+      <c r="S20" s="3">
+        <v>229.2594217795833</v>
+      </c>
+      <c r="T20" s="3">
+        <v>3.639672807270585</v>
+      </c>
+      <c r="U20" s="3">
+        <v>5.713564694396527</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0.5290540528382506</v>
+      </c>
+      <c r="W20" s="3">
         <v>3.406800000000001</v>
       </c>
-      <c r="K20" s="3">
+      <c r="X20" s="3">
         <v>-5.255653338394686</v>
       </c>
-      <c r="L20" s="3">
+      <c r="Y20" s="3">
         <v>5.550686018365157E-06</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N20" s="3">
+      <c r="AA20" s="3">
         <v>28.10703659057617</v>
       </c>
-      <c r="O20" s="3">
+      <c r="AB20" s="3">
         <v>28.69431114196777</v>
       </c>
-      <c r="P20" s="3">
+      <c r="AC20" s="3">
         <v>48.72861862182617</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0.1811548173427582</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0.6515179872512817</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0.6622465252876282</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0.09961003810167313</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0.9535791277885437</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0.1615897864103317</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>0.2876680791378021</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>0.4636885225772858</v>
+      </c>
+      <c r="AO20" s="3">
+        <v>0.4422608017921448</v>
+      </c>
+      <c r="AP20" s="3">
+        <v>0.9085427522659302</v>
+      </c>
+      <c r="AQ20" s="3">
+        <v>0.9986909627914429</v>
+      </c>
+      <c r="AR20" s="3">
+        <v>0.7246156930923462</v>
+      </c>
+      <c r="AS20" s="3">
+        <v>0.8257194757461548</v>
+      </c>
+      <c r="AT20" s="3">
+        <v>0.8465056419372559</v>
+      </c>
+      <c r="AU20" s="3">
+        <v>-5.251671314239502</v>
+      </c>
+      <c r="AV20" s="3">
+        <v>95.00550842285156</v>
+      </c>
+      <c r="AW20" s="3">
+        <v>11.14853286743164</v>
+      </c>
+      <c r="AX20" s="3">
+        <v>431.5840000000002</v>
+      </c>
+      <c r="AY20" s="3">
+        <v>3.406800000000001</v>
+      </c>
+      <c r="AZ20" s="3">
+        <v>0.3984526300599843</v>
+      </c>
+      <c r="BA20" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB20" s="3">
+        <v>3.435578253721044</v>
+      </c>
+      <c r="BC20" s="3">
+        <v>0.7293801940309952</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2375,45 +4984,170 @@
         <v>10.1</v>
       </c>
       <c r="G21" s="3">
-        <v>0.6976196057554538</v>
-      </c>
-      <c r="H21" s="3">
-        <v>4.984477107800576</v>
+        <v>5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I21" s="3">
-        <v>5.302380394244546</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J21" s="3">
+        <v>4.984477127902903</v>
+      </c>
+      <c r="K21" s="3">
+        <v>5.302380392493043</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1.357417897250621</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0.5417904351222217</v>
+      </c>
+      <c r="N21" s="3">
+        <v>53.01812858399423</v>
+      </c>
+      <c r="O21" s="3">
+        <v>73.94508612551861</v>
+      </c>
+      <c r="P21" s="3">
+        <v>4.64258210274938</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0.5417904351222217</v>
+      </c>
+      <c r="R21" s="3">
+        <v>1.974734185099057</v>
+      </c>
+      <c r="S21" s="3">
+        <v>262.6196088127128</v>
+      </c>
+      <c r="T21" s="3">
+        <v>3.580672849909825</v>
+      </c>
+      <c r="U21" s="3">
+        <v>5.704491355588933</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0.5417904351222217</v>
+      </c>
+      <c r="W21" s="3">
         <v>3.277400000000002</v>
       </c>
-      <c r="K21" s="3">
+      <c r="X21" s="3">
         <v>-5.163132274527731</v>
       </c>
-      <c r="L21" s="3">
+      <c r="Y21" s="3">
         <v>6.868592091385286E-06</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N21" s="3">
+      <c r="AA21" s="3">
         <v>22.30717849731445</v>
       </c>
-      <c r="O21" s="3">
+      <c r="AB21" s="3">
         <v>20.03717041015625</v>
       </c>
-      <c r="P21" s="3">
+      <c r="AC21" s="3">
         <v>52.28086471557617</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>0.1634544134140015</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0.69719398021698</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>0.6966174840927124</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>0.08969704806804657</v>
+      </c>
+      <c r="AK21" s="3">
+        <v>0.9630613327026367</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>0.2257703840732574</v>
+      </c>
+      <c r="AM21" s="3">
+        <v>0.3366061151027679</v>
+      </c>
+      <c r="AN21" s="3">
+        <v>0.5271130800247192</v>
+      </c>
+      <c r="AO21" s="3">
+        <v>0.4627062678337097</v>
+      </c>
+      <c r="AP21" s="3">
+        <v>0.9494125247001648</v>
+      </c>
+      <c r="AQ21" s="3">
+        <v>0.9993936419487</v>
+      </c>
+      <c r="AR21" s="3">
+        <v>0.7522884607315063</v>
+      </c>
+      <c r="AS21" s="3">
+        <v>0.8586667776107788</v>
+      </c>
+      <c r="AT21" s="3">
+        <v>0.8462157249450684</v>
+      </c>
+      <c r="AU21" s="3">
+        <v>-5.302098274230957</v>
+      </c>
+      <c r="AV21" s="3">
+        <v>92.66982269287109</v>
+      </c>
+      <c r="AW21" s="3">
+        <v>12.74984073638916</v>
+      </c>
+      <c r="AX21" s="3">
+        <v>431.5840000000002</v>
+      </c>
+      <c r="AY21" s="3">
+        <v>3.277400000000002</v>
+      </c>
+      <c r="AZ21" s="3">
+        <v>0.4171516579949314</v>
+      </c>
+      <c r="BA21" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB21" s="3">
+        <v>3.436364897846149</v>
+      </c>
+      <c r="BC21" s="3">
+        <v>0.7292927891282057</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="92" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(Cc4cc(F)cc(C(=O)NC)c4)C3)C2)c1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN(Cc4cc(NC)cc(C(N)=O)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2425,44 +5159,169 @@
         <v>1</v>
       </c>
       <c r="E22" s="3">
-        <v>0.5714285714285714</v>
+        <v>0.6101694915254238</v>
       </c>
       <c r="F22" s="3">
-        <v>10.37</v>
+        <v>10.74</v>
       </c>
       <c r="G22" s="3">
-        <v>0.6976196057554538</v>
-      </c>
-      <c r="H22" s="3">
-        <v>4.984477107800576</v>
+        <v>5</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I22" s="3">
-        <v>5.302380394244546</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J22" s="3">
-        <v>3.444200000000002</v>
+        <v>4.984477127902903</v>
       </c>
       <c r="K22" s="3">
-        <v>-5.222354611521923</v>
+        <v>5.302380392493043</v>
       </c>
       <c r="L22" s="3">
-        <v>5.993015328130731E-06</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
+        <v>1.317032321907858</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0.5470367383247328</v>
+      </c>
+      <c r="N22" s="3">
+        <v>51.24377626532831</v>
+      </c>
+      <c r="O22" s="3">
+        <v>74.71041793425144</v>
+      </c>
+      <c r="P22" s="3">
+        <v>4.682967678092142</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0.5470367383247328</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1.757277363984813</v>
+      </c>
+      <c r="S22" s="3">
+        <v>245.0328599583538</v>
+      </c>
+      <c r="T22" s="3">
+        <v>3.610775670975666</v>
+      </c>
+      <c r="U22" s="3">
+        <v>5.755159685208618</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0.5470367383247328</v>
+      </c>
+      <c r="W22" s="3">
+        <v>3.476200000000001</v>
+      </c>
+      <c r="X22" s="3">
+        <v>-5.307125510687144</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>4.930312977934696E-06</v>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N22" s="3">
-        <v>24.07105827331543</v>
-      </c>
-      <c r="O22" s="3">
-        <v>23.2003173828125</v>
-      </c>
-      <c r="P22" s="3">
-        <v>48.26595687866211</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="AA22" s="3">
+        <v>31.98368453979492</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>31.56573486328125</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>51.06867218017578</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0.1960595548152924</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0.6519122719764709</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0.636513352394104</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0.1000093072652817</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0.9555538296699524</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0.2145793437957764</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>0.2550626397132874</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0.3734226822853088</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0.4869077205657959</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0.8911203145980835</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0.9990541338920593</v>
+      </c>
+      <c r="AR22" s="3">
+        <v>0.7657650113105774</v>
+      </c>
+      <c r="AS22" s="3">
+        <v>0.8602112531661987</v>
+      </c>
+      <c r="AT22" s="3">
+        <v>0.8396522402763367</v>
+      </c>
+      <c r="AU22" s="3">
+        <v>-5.287175178527832</v>
+      </c>
+      <c r="AV22" s="3">
+        <v>93.91284942626953</v>
+      </c>
+      <c r="AW22" s="3">
+        <v>12.82140350341797</v>
+      </c>
+      <c r="AX22" s="3">
+        <v>431.5840000000002</v>
+      </c>
+      <c r="AY22" s="3">
+        <v>3.476200000000001</v>
+      </c>
+      <c r="AZ22" s="3">
+        <v>0.5186613605993676</v>
+      </c>
+      <c r="BA22" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB22" s="3">
+        <v>3.46516489784615</v>
+      </c>
+      <c r="BC22" s="3">
+        <v>0.7260927891282056</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="3">
         <v>1</v>
       </c>
     </row>

--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/plain/mol2mol_scaffold_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/plain/mol2mol_scaffold_plain_generated_optimal.xlsx
@@ -1586,7 +1586,7 @@
         <v>278.8545515586202</v>
       </c>
       <c r="T2" s="3">
-        <v>3.554622262412655</v>
+        <v>3.554622262412656</v>
       </c>
       <c r="U2" s="3">
         <v>5.829204178560643</v>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>23.21879959106445</v>
+        <v>23.2188</v>
       </c>
       <c r="AB2" s="3">
-        <v>26.07429504394531</v>
+        <v>26.074295</v>
       </c>
       <c r="AC2" s="3">
-        <v>42.78295135498047</v>
+        <v>42.78295</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -1627,55 +1627,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.1793070733547211</v>
+        <v>0.17930707</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.6316912174224854</v>
+        <v>0.6316912</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.6344318389892578</v>
+        <v>0.63443184</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.09223626554012299</v>
+        <v>0.092236266</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.9331738352775574</v>
+        <v>0.93317384</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.1351944208145142</v>
+        <v>0.13519442</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.2133276015520096</v>
+        <v>0.2133276</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.3550845980644226</v>
+        <v>0.3550846</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.3897414803504944</v>
+        <v>0.38974148</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.8482101559638977</v>
+        <v>0.84821016</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9978948831558228</v>
+        <v>0.9978949</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.7498563528060913</v>
+        <v>0.7498563499999999</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.783575713634491</v>
+        <v>0.7835757</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.7166632413864136</v>
+        <v>0.71666324</v>
       </c>
       <c r="AU2" s="3">
-        <v>-5.260924339294434</v>
+        <v>-5.2609243</v>
       </c>
       <c r="AV2" s="3">
-        <v>92.48931884765625</v>
+        <v>92.48932000000001</v>
       </c>
       <c r="AW2" s="3">
-        <v>10.36054039001465</v>
+        <v>10.36054</v>
       </c>
       <c r="AX2" s="3">
         <v>417.5570000000002</v>
@@ -1790,13 +1790,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>62.39081573486328</v>
+        <v>62.390816</v>
       </c>
       <c r="AB3" s="3">
-        <v>57.58205413818359</v>
+        <v>57.582054</v>
       </c>
       <c r="AC3" s="3">
-        <v>51.68029022216797</v>
+        <v>51.68029</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1808,55 +1808,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.0497056320309639</v>
+        <v>0.049705632</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.2396424263715744</v>
+        <v>0.23964243</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.8849323391914368</v>
+        <v>0.88493234</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.08105399459600449</v>
+        <v>0.081053995</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.8425236940383911</v>
+        <v>0.8425237</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.2971973717212677</v>
+        <v>0.29719737</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.7376928329467773</v>
+        <v>0.73769283</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.8714698553085327</v>
+        <v>0.87146986</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.1994397044181824</v>
+        <v>0.1994397</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9584705233573914</v>
+        <v>0.9584705</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9998761415481567</v>
+        <v>0.99987614</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7683823108673096</v>
+        <v>0.7683823</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.9477031826972961</v>
+        <v>0.9477032</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.8606225848197937</v>
+        <v>0.8606226</v>
       </c>
       <c r="AU3" s="3">
-        <v>-4.662340641021729</v>
+        <v>-4.6623406</v>
       </c>
       <c r="AV3" s="3">
-        <v>99.64119720458984</v>
+        <v>99.6412</v>
       </c>
       <c r="AW3" s="3">
-        <v>6.217146873474121</v>
+        <v>6.217147</v>
       </c>
       <c r="AX3" s="3">
         <v>421.4720000000002</v>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>54.03301239013672</v>
+        <v>54.033012</v>
       </c>
       <c r="AB4" s="3">
-        <v>51.58975982666016</v>
+        <v>51.58976</v>
       </c>
       <c r="AC4" s="3">
-        <v>46.11928939819336</v>
+        <v>46.11929</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -1989,55 +1989,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.1514938771724701</v>
+        <v>0.15149388</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.3794128894805908</v>
+        <v>0.3794129</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.790505588054657</v>
+        <v>0.7905056</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.05281468108296394</v>
+        <v>0.05281468</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.8946078419685364</v>
+        <v>0.89460784</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.4100111424922943</v>
+        <v>0.41001114</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.6163969039916992</v>
+        <v>0.6163969</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.7340325713157654</v>
+        <v>0.7340326</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.2590197920799255</v>
+        <v>0.2590198</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9837437868118286</v>
+        <v>0.9837437999999999</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.7540546655654907</v>
+        <v>0.75405467</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.9556649327278137</v>
+        <v>0.95566493</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.8375112414360046</v>
+        <v>0.83751124</v>
       </c>
       <c r="AU4" s="3">
-        <v>-4.578262329101562</v>
+        <v>-4.5782623</v>
       </c>
       <c r="AV4" s="3">
-        <v>98.41603851318359</v>
+        <v>98.41604</v>
       </c>
       <c r="AW4" s="3">
-        <v>6.461911201477051</v>
+        <v>6.461911</v>
       </c>
       <c r="AX4" s="3">
         <v>421.4720000000002</v>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>54.02365875244141</v>
+        <v>54.02366</v>
       </c>
       <c r="AB5" s="3">
-        <v>51.60739898681641</v>
+        <v>51.6074</v>
       </c>
       <c r="AC5" s="3">
-        <v>46.01802825927734</v>
+        <v>46.01803</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -2170,55 +2170,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.1515597701072693</v>
+        <v>0.15155977</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.3794240057468414</v>
+        <v>0.379424</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.7904849052429199</v>
+        <v>0.7904849</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.0527871660888195</v>
+        <v>0.052787166</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.8945648074150085</v>
+        <v>0.8945648</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.409633457660675</v>
+        <v>0.40963346</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.6159688234329224</v>
+        <v>0.6159688</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.7336847186088562</v>
+        <v>0.7336847</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.2587462067604065</v>
+        <v>0.2587462</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9837337732315063</v>
+        <v>0.9837338</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.7541525959968567</v>
+        <v>0.7541526</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.955665111541748</v>
+        <v>0.9556651</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8373624682426453</v>
+        <v>0.83736247</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.578091621398926</v>
+        <v>-4.5780916</v>
       </c>
       <c r="AV5" s="3">
-        <v>98.40773010253906</v>
+        <v>98.40773</v>
       </c>
       <c r="AW5" s="3">
-        <v>6.452359676361084</v>
+        <v>6.4523597</v>
       </c>
       <c r="AX5" s="3">
         <v>420.4749380000002</v>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>49.53058624267578</v>
+        <v>49.530586</v>
       </c>
       <c r="AB6" s="3">
-        <v>50.50267791748047</v>
+        <v>50.502678</v>
       </c>
       <c r="AC6" s="3">
-        <v>42.52790069580078</v>
+        <v>42.5279</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2351,55 +2351,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.1503766477108002</v>
+        <v>0.15037665</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.4014430642127991</v>
+        <v>0.40144306</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.7944496870040894</v>
+        <v>0.7944497</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.06801829487085342</v>
+        <v>0.06801829500000001</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.9175645112991333</v>
+        <v>0.9175645</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.4286567568778992</v>
+        <v>0.42865676</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.7177208662033081</v>
+        <v>0.71772087</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.8529923558235168</v>
+        <v>0.85299236</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.3775244355201721</v>
+        <v>0.37752444</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9936367273330688</v>
+        <v>0.9936367</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9999710321426392</v>
+        <v>0.99997103</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.653423011302948</v>
+        <v>0.653423</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.936070442199707</v>
+        <v>0.9360704399999999</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.899492084980011</v>
+        <v>0.8994921</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.60943078994751</v>
+        <v>-4.609431</v>
       </c>
       <c r="AV6" s="3">
-        <v>99.28874969482422</v>
+        <v>99.28874999999999</v>
       </c>
       <c r="AW6" s="3">
-        <v>4.949751853942871</v>
+        <v>4.949752</v>
       </c>
       <c r="AX6" s="3">
         <v>445.4940000000003</v>
@@ -2414,7 +2414,7 @@
         <v>4</v>
       </c>
       <c r="BB6" s="3">
-        <v>3.712554966519908</v>
+        <v>3.712554966519909</v>
       </c>
       <c r="BC6" s="3">
         <v>0.6986050037200102</v>
@@ -2467,7 +2467,7 @@
         <v>5.442375258869468</v>
       </c>
       <c r="L7" s="3">
-        <v>0.9042563426665993</v>
+        <v>0.9042563426665992</v>
       </c>
       <c r="M7" s="3">
         <v>0.2814547288330222</v>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>62.37113189697266</v>
+        <v>62.37113</v>
       </c>
       <c r="AB7" s="3">
-        <v>55.22406768798828</v>
+        <v>55.224068</v>
       </c>
       <c r="AC7" s="3">
-        <v>42.23021697998047</v>
+        <v>42.230217</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -2532,55 +2532,55 @@
         <v>1</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.3101035356521606</v>
+        <v>0.31010354</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3923474252223969</v>
+        <v>0.39234743</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.8259280920028687</v>
+        <v>0.8259281000000001</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.06683068722486496</v>
+        <v>0.06683069</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.89606773853302</v>
+        <v>0.89606774</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.3563960790634155</v>
+        <v>0.35639608</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.6407725214958191</v>
+        <v>0.6407725</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.7509437799453735</v>
+        <v>0.7509438000000001</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.298628181219101</v>
+        <v>0.29862818</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9887466430664062</v>
+        <v>0.98874664</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.999965488910675</v>
+        <v>0.9999655</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.7102676630020142</v>
+        <v>0.71026766</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9408232569694519</v>
+        <v>0.9408232600000001</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8539096117019653</v>
+        <v>0.8539096</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.659994602203369</v>
+        <v>-4.6599946</v>
       </c>
       <c r="AV7" s="3">
-        <v>99.01403045654297</v>
+        <v>99.01403000000001</v>
       </c>
       <c r="AW7" s="3">
-        <v>5.339962959289551</v>
+        <v>5.339963</v>
       </c>
       <c r="AX7" s="3">
         <v>441.8900000000002</v>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>67.9300537109375</v>
+        <v>67.93004999999999</v>
       </c>
       <c r="AB8" s="3">
-        <v>55.20512771606445</v>
+        <v>55.205128</v>
       </c>
       <c r="AC8" s="3">
-        <v>40.69405746459961</v>
+        <v>40.694057</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -2713,55 +2713,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.2426724880933762</v>
+        <v>0.24267249</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.5274170637130737</v>
+        <v>0.52741706</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.8195544481277466</v>
+        <v>0.81955445</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.05707133933901787</v>
+        <v>0.05707134</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.9460126757621765</v>
+        <v>0.9460127</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.3255794644355774</v>
+        <v>0.32557946</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.6021593809127808</v>
+        <v>0.6021594</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.7146463990211487</v>
+        <v>0.7146464</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.2755510210990906</v>
+        <v>0.27555102</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9880801439285278</v>
+        <v>0.98808014</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.9999575614929199</v>
+        <v>0.99995756</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.7738900184631348</v>
+        <v>0.77389</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.9560348391532898</v>
+        <v>0.9560348400000001</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.9067276120185852</v>
+        <v>0.9067276</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.787168502807617</v>
+        <v>-4.7871685</v>
       </c>
       <c r="AV8" s="3">
-        <v>100.1134414672852</v>
+        <v>100.11344</v>
       </c>
       <c r="AW8" s="3">
-        <v>7.336749076843262</v>
+        <v>7.336749</v>
       </c>
       <c r="AX8" s="3">
         <v>446.5510000000002</v>
@@ -2847,7 +2847,7 @@
         <v>0.5761692979434486</v>
       </c>
       <c r="R9" s="3">
-        <v>1.285738747074785</v>
+        <v>1.285738747074784</v>
       </c>
       <c r="S9" s="3">
         <v>233.2042065343045</v>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>50.03407287597656</v>
+        <v>50.034073</v>
       </c>
       <c r="AB9" s="3">
-        <v>47.67665863037109</v>
+        <v>47.67666</v>
       </c>
       <c r="AC9" s="3">
-        <v>41.62461090087891</v>
+        <v>41.62461</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -2894,55 +2894,55 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.2527405917644501</v>
+        <v>0.2527406</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.4688826203346252</v>
+        <v>0.46888262</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.8351690173149109</v>
+        <v>0.8351690000000001</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.04883065074682236</v>
+        <v>0.04883065</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.9386070370674133</v>
+        <v>0.9386070399999999</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.3703396916389465</v>
+        <v>0.3703397</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.6521976590156555</v>
+        <v>0.65219766</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.7791668176651001</v>
+        <v>0.7791668</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.2660719156265259</v>
+        <v>0.26607192</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9907934069633484</v>
+        <v>0.9907934</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9999765157699585</v>
+        <v>0.9999765</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.7638531923294067</v>
+        <v>0.7638532</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9541949033737183</v>
+        <v>0.9541949</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8792737722396851</v>
+        <v>0.8792738</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.85697603225708</v>
+        <v>-4.856976</v>
       </c>
       <c r="AV9" s="3">
-        <v>99.01522064208984</v>
+        <v>99.01522</v>
       </c>
       <c r="AW9" s="3">
-        <v>8.199435234069824</v>
+        <v>8.199434999999999</v>
       </c>
       <c r="AX9" s="3">
         <v>432.5240000000002</v>
@@ -3022,7 +3022,7 @@
         <v>76.0808612751983</v>
       </c>
       <c r="P10" s="3">
-        <v>4.797356000773195</v>
+        <v>4.797356000773196</v>
       </c>
       <c r="Q10" s="3">
         <v>0.6027867767415637</v>
@@ -3034,7 +3034,7 @@
         <v>242.1620484371657</v>
       </c>
       <c r="T10" s="3">
-        <v>3.61589391835973</v>
+        <v>3.615893918359729</v>
       </c>
       <c r="U10" s="3">
         <v>5.97881808318666</v>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>59.47090530395508</v>
+        <v>59.470905</v>
       </c>
       <c r="AB10" s="3">
-        <v>57.21721267700195</v>
+        <v>57.217213</v>
       </c>
       <c r="AC10" s="3">
-        <v>40.80252838134766</v>
+        <v>40.80253</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -3075,55 +3075,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.1844686716794968</v>
+        <v>0.18446867</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.4202435612678528</v>
+        <v>0.42024356</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.8358316421508789</v>
+        <v>0.83583164</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.04515016824007034</v>
+        <v>0.04515017</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.9386307597160339</v>
+        <v>0.93863076</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.4181106984615326</v>
+        <v>0.4181107</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.7442826628684998</v>
+        <v>0.74428266</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.8617993593215942</v>
+        <v>0.86179936</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.2975649237632751</v>
+        <v>0.29756492</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9936869740486145</v>
+        <v>0.993687</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9999872446060181</v>
+        <v>0.9999872400000001</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.721790075302124</v>
+        <v>0.7217901</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.957022488117218</v>
+        <v>0.9570225</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.9055355191230774</v>
+        <v>0.9055355</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.767285823822021</v>
+        <v>-4.767286</v>
       </c>
       <c r="AV10" s="3">
-        <v>101.1879043579102</v>
+        <v>101.187904</v>
       </c>
       <c r="AW10" s="3">
-        <v>5.74851131439209</v>
+        <v>5.7485113</v>
       </c>
       <c r="AX10" s="3">
         <v>432.5240000000002</v>
@@ -3200,7 +3200,7 @@
         <v>14.9370461103721</v>
       </c>
       <c r="O11" s="3">
-        <v>9.749179286565441</v>
+        <v>9.74917928656544</v>
       </c>
       <c r="P11" s="3">
         <v>4.937192743725992</v>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>12.38687324523926</v>
+        <v>12.386873</v>
       </c>
       <c r="AB11" s="3">
-        <v>28.63481521606445</v>
+        <v>28.634815</v>
       </c>
       <c r="AC11" s="3">
-        <v>41.37298583984375</v>
+        <v>41.372986</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3256,55 +3256,55 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.1577767580747604</v>
+        <v>0.15777676</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.5154687762260437</v>
+        <v>0.5154687999999999</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.3734657168388367</v>
+        <v>0.37346572</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.09895943105220795</v>
+        <v>0.09895943</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9235855340957642</v>
+        <v>0.92358553</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.0505656786262989</v>
+        <v>0.05056568</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.1717598289251328</v>
+        <v>0.17175983</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.1719331741333008</v>
+        <v>0.17193317</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.4868618547916412</v>
+        <v>0.48686185</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.6581208109855652</v>
+        <v>0.6581208</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9986150860786438</v>
+        <v>0.9986151</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7258269190788269</v>
+        <v>0.7258269000000001</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.8411421775817871</v>
+        <v>0.8411422</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.7036873698234558</v>
+        <v>0.70368737</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.742566585540771</v>
+        <v>-4.7425666</v>
       </c>
       <c r="AV11" s="3">
-        <v>86.36440277099609</v>
+        <v>86.3644</v>
       </c>
       <c r="AW11" s="3">
-        <v>11.66602993011475</v>
+        <v>11.66603</v>
       </c>
       <c r="AX11" s="3">
         <v>411.4960000000001</v>
@@ -3378,7 +3378,7 @@
         <v>0.5538972903245317</v>
       </c>
       <c r="N12" s="3">
-        <v>52.85744973393292</v>
+        <v>52.85744973393293</v>
       </c>
       <c r="O12" s="3">
         <v>73.97049186169482</v>
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>39.75581741333008</v>
+        <v>39.755817</v>
       </c>
       <c r="AB12" s="3">
-        <v>32.81678771972656</v>
+        <v>32.816788</v>
       </c>
       <c r="AC12" s="3">
-        <v>42.63826751708984</v>
+        <v>42.638268</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -3437,55 +3437,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.3349597156047821</v>
+        <v>0.33495972</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.4971658289432526</v>
+        <v>0.49716583</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.8305774927139282</v>
+        <v>0.8305775</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.05206187814474106</v>
+        <v>0.05206188</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.9213894605636597</v>
+        <v>0.92138946</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.2205078601837158</v>
+        <v>0.22050786</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.4619075655937195</v>
+        <v>0.46190757</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.5620790719985962</v>
+        <v>0.5620791000000001</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.1509415358304977</v>
+        <v>0.15094154</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.957487940788269</v>
+        <v>0.95748794</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9998504519462585</v>
+        <v>0.9998504499999999</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.8074136972427368</v>
+        <v>0.8074137</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.9490911364555359</v>
+        <v>0.9490911400000001</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.8077398538589478</v>
+        <v>0.80773985</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.965895175933838</v>
+        <v>-4.965895</v>
       </c>
       <c r="AV12" s="3">
-        <v>95.56562805175781</v>
+        <v>95.56563</v>
       </c>
       <c r="AW12" s="3">
-        <v>10.71188068389893</v>
+        <v>10.711881</v>
       </c>
       <c r="AX12" s="3">
         <v>417.5570000000001</v>
@@ -3600,13 +3600,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>38.1949577331543</v>
+        <v>38.194958</v>
       </c>
       <c r="AB13" s="3">
-        <v>46.53000640869141</v>
+        <v>46.530006</v>
       </c>
       <c r="AC13" s="3">
-        <v>52.06615447998047</v>
+        <v>52.066154</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -3618,55 +3618,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.14383664727211</v>
+        <v>0.14383665</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.2526366710662842</v>
+        <v>0.25263667</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.7948338389396667</v>
+        <v>0.79483384</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.05038211867213249</v>
+        <v>0.05038212</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.7190860509872437</v>
+        <v>0.71908605</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.1829346120357513</v>
+        <v>0.18293461</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.3825122117996216</v>
+        <v>0.3825122</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.4498942494392395</v>
+        <v>0.44989425</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.06359347701072693</v>
+        <v>0.06359347999999999</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.8871018290519714</v>
+        <v>0.8871018000000001</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9999326467514038</v>
+        <v>0.99993265</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.8340275883674622</v>
+        <v>0.8340276</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.9630118608474731</v>
+        <v>0.9630118600000001</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.621238112449646</v>
+        <v>0.6212381</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.4007568359375</v>
+        <v>-4.400757</v>
       </c>
       <c r="AV13" s="3">
-        <v>87.47709655761719</v>
+        <v>87.47709999999999</v>
       </c>
       <c r="AW13" s="3">
-        <v>9.734238624572754</v>
+        <v>9.734239000000001</v>
       </c>
       <c r="AX13" s="3">
         <v>411.4520000000001</v>
@@ -3734,7 +3734,7 @@
         <v>5.373032676973282</v>
       </c>
       <c r="L14" s="3">
-        <v>0.9412992172191981</v>
+        <v>0.941299217219198</v>
       </c>
       <c r="M14" s="3">
         <v>0.3091094834936228</v>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>44.03082275390625</v>
+        <v>44.030823</v>
       </c>
       <c r="AB14" s="3">
-        <v>52.285888671875</v>
+        <v>52.28589</v>
       </c>
       <c r="AC14" s="3">
-        <v>46.47860336303711</v>
+        <v>46.478603</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -3799,55 +3799,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.1481298804283142</v>
+        <v>0.14812988</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.2408362925052643</v>
+        <v>0.24083629</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.7796632647514343</v>
+        <v>0.77966326</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.04402393475174904</v>
+        <v>0.044023935</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.6242526769638062</v>
+        <v>0.6242527</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.1550628244876862</v>
+        <v>0.15506282</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.2458717375993729</v>
+        <v>0.24587174</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.2648356854915619</v>
+        <v>0.2648357</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.03013483621180058</v>
+        <v>0.030134836</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.7748692631721497</v>
+        <v>0.77486926</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9999569058418274</v>
+        <v>0.9999569</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.8821442723274231</v>
+        <v>0.8821443</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.9609131813049316</v>
+        <v>0.9609132</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.4224107265472412</v>
+        <v>0.42241073</v>
       </c>
       <c r="AU14" s="3">
-        <v>-4.425469398498535</v>
+        <v>-4.4254694</v>
       </c>
       <c r="AV14" s="3">
-        <v>90.94108581542969</v>
+        <v>90.941086</v>
       </c>
       <c r="AW14" s="3">
-        <v>7.25708532333374</v>
+        <v>7.2570853</v>
       </c>
       <c r="AX14" s="3">
         <v>367.3990000000001</v>
@@ -3962,13 +3962,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>46.68682098388672</v>
+        <v>46.68682</v>
       </c>
       <c r="AB15" s="3">
-        <v>46.50349807739258</v>
+        <v>46.503498</v>
       </c>
       <c r="AC15" s="3">
-        <v>40.06744003295898</v>
+        <v>40.06744</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -3980,55 +3980,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.1574867814779282</v>
+        <v>0.15748678</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.357526034116745</v>
+        <v>0.35752603</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.7977760434150696</v>
+        <v>0.79777604</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.05292393639683723</v>
+        <v>0.052923936</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.86536705493927</v>
+        <v>0.86536705</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.3862963616847992</v>
+        <v>0.38629636</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.5458816289901733</v>
+        <v>0.5458816</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.6691521406173706</v>
+        <v>0.66915214</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.2068126946687698</v>
+        <v>0.2068127</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9757219552993774</v>
+        <v>0.97572196</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9999698400497437</v>
+        <v>0.99996984</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.7815946936607361</v>
+        <v>0.7815947</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.9552289843559265</v>
+        <v>0.955229</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.7651858329772949</v>
+        <v>0.76518583</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.575211524963379</v>
+        <v>-4.5752115</v>
       </c>
       <c r="AV15" s="3">
-        <v>96.03324890136719</v>
+        <v>96.03325</v>
       </c>
       <c r="AW15" s="3">
-        <v>5.789505958557129</v>
+        <v>5.789506</v>
       </c>
       <c r="AX15" s="3">
         <v>407.4450000000002</v>
@@ -4099,7 +4099,7 @@
         <v>0.938415746718696</v>
       </c>
       <c r="M16" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="N16" s="3">
         <v>9.948615853378566</v>
@@ -4111,7 +4111,7 @@
         <v>5.061584253281304</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="R16" s="3">
         <v>2.974292526811678</v>
@@ -4126,7 +4126,7 @@
         <v>5.526616320100387</v>
       </c>
       <c r="V16" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="W16" s="3">
         <v>3.314000000000002</v>
@@ -4135,7 +4135,7 @@
         <v>-5.017454811696665</v>
       </c>
       <c r="Y16" s="3">
-        <v>9.606057641337639E-06</v>
+        <v>9.60605764133764E-06</v>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
@@ -4143,13 +4143,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>32.87833404541016</v>
+        <v>32.878334</v>
       </c>
       <c r="AB16" s="3">
-        <v>23.18183326721191</v>
+        <v>23.181833</v>
       </c>
       <c r="AC16" s="3">
-        <v>52.3669548034668</v>
+        <v>52.366955</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -4161,55 +4161,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.1258585155010223</v>
+        <v>0.12585852</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.2497570961713791</v>
+        <v>0.2497571</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.8550773859024048</v>
+        <v>0.8550774</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.06400169432163239</v>
+        <v>0.064001694</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.6612062454223633</v>
+        <v>0.66120625</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.2865390479564667</v>
+        <v>0.28653905</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.342566967010498</v>
+        <v>0.34256697</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.4608745574951172</v>
+        <v>0.46087456</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.05450470373034477</v>
+        <v>0.054504704</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.763884425163269</v>
+        <v>0.7638844</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9998586773872375</v>
+        <v>0.9998587</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.8826817274093628</v>
+        <v>0.8826817</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.9536167979240417</v>
+        <v>0.9536168</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.5413268208503723</v>
+        <v>0.5413268</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.699678897857666</v>
+        <v>-4.699679</v>
       </c>
       <c r="AV16" s="3">
-        <v>97.27809143066406</v>
+        <v>97.27809000000001</v>
       </c>
       <c r="AW16" s="3">
-        <v>4.346566200256348</v>
+        <v>4.346566</v>
       </c>
       <c r="AX16" s="3">
         <v>401.3880000000001</v>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>27.08931350708008</v>
+        <v>27.089314</v>
       </c>
       <c r="AB17" s="3">
-        <v>20.42182159423828</v>
+        <v>20.421822</v>
       </c>
       <c r="AC17" s="3">
-        <v>50.60114288330078</v>
+        <v>50.601143</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -4342,58 +4342,58 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.1081468015909195</v>
+        <v>0.1081468</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.3498961627483368</v>
+        <v>0.34989616</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.8508683443069458</v>
+        <v>0.85086834</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.04858251661062241</v>
+        <v>0.048582517</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.8946163058280945</v>
+        <v>0.8946163</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.277321994304657</v>
+        <v>0.277322</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.6814661026000977</v>
+        <v>0.6814661</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.8180168867111206</v>
+        <v>0.8180169</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.2221898287534714</v>
+        <v>0.22218983</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.9871047139167786</v>
+        <v>0.9871046999999999</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9999736547470093</v>
+        <v>0.99997365</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.761349618434906</v>
+        <v>0.7613496</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9597161412239075</v>
+        <v>0.9597161400000001</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.8450393676757812</v>
+        <v>0.84503937</v>
       </c>
       <c r="AU17" s="3">
-        <v>-4.713494300842285</v>
+        <v>-4.7134943</v>
       </c>
       <c r="AV17" s="3">
-        <v>97.13545227050781</v>
+        <v>97.13545000000001</v>
       </c>
       <c r="AW17" s="3">
-        <v>5.66744327545166</v>
+        <v>5.6674433</v>
       </c>
       <c r="AX17" s="3">
-        <v>472.4670000000003</v>
+        <v>472.4670000000002</v>
       </c>
       <c r="AY17" s="3">
         <v>3.439000000000003</v>
@@ -4479,7 +4479,7 @@
         <v>1.941800432483435</v>
       </c>
       <c r="S18" s="3">
-        <v>233.3246509673746</v>
+        <v>233.3246509673747</v>
       </c>
       <c r="T18" s="3">
         <v>3.63203937516447</v>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>17.603271484375</v>
+        <v>17.603271</v>
       </c>
       <c r="AB18" s="3">
-        <v>15.00508689880371</v>
+        <v>15.005087</v>
       </c>
       <c r="AC18" s="3">
-        <v>60.3412971496582</v>
+        <v>60.341297</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -4523,55 +4523,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.1759376376867294</v>
+        <v>0.17593764</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.3225483298301697</v>
+        <v>0.32254833</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.8475942611694336</v>
+        <v>0.84759426</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.0409967452287674</v>
+        <v>0.040996745</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.850246250629425</v>
+        <v>0.85024625</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.1296553909778595</v>
+        <v>0.12965539</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.3709774911403656</v>
+        <v>0.3709775</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.5289421081542969</v>
+        <v>0.5289421</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.06528114527463913</v>
+        <v>0.065281145</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.9636019468307495</v>
+        <v>0.96360195</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.999913215637207</v>
+        <v>0.9999131999999999</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.8498846292495728</v>
+        <v>0.8498846</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9663764238357544</v>
+        <v>0.9663764</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.7521975040435791</v>
+        <v>0.7521975</v>
       </c>
       <c r="AU18" s="3">
-        <v>-4.828359127044678</v>
+        <v>-4.828359</v>
       </c>
       <c r="AV18" s="3">
-        <v>92.74420928955078</v>
+        <v>92.74421</v>
       </c>
       <c r="AW18" s="3">
-        <v>11.26456642150879</v>
+        <v>11.264566</v>
       </c>
       <c r="AX18" s="3">
         <v>458.4840000000002</v>
@@ -4580,7 +4580,7 @@
         <v>3.423100000000002</v>
       </c>
       <c r="AZ18" s="3">
-        <v>0.4319787741095225</v>
+        <v>0.4319787741095224</v>
       </c>
       <c r="BA18" s="3">
         <v>4</v>
@@ -4648,7 +4648,7 @@
         <v>12.12319990519978</v>
       </c>
       <c r="O19" s="3">
-        <v>11.30303816696889</v>
+        <v>11.3030381669689</v>
       </c>
       <c r="P19" s="3">
         <v>5.04820129151144</v>
@@ -4686,13 +4686,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>24.07105827331543</v>
+        <v>24.071058</v>
       </c>
       <c r="AB19" s="3">
-        <v>23.20031547546387</v>
+        <v>23.200315</v>
       </c>
       <c r="AC19" s="3">
-        <v>48.26595687866211</v>
+        <v>48.265957</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -4704,55 +4704,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.1182065233588219</v>
+        <v>0.11820652</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.6393347382545471</v>
+        <v>0.63933474</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.604170024394989</v>
+        <v>0.60417</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.1051495298743248</v>
+        <v>0.10514953</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.9317499995231628</v>
+        <v>0.93175</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.1908909529447556</v>
+        <v>0.19089095</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.2398413419723511</v>
+        <v>0.23984134</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.3507117331027985</v>
+        <v>0.35071173</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.4600063264369965</v>
+        <v>0.46000633</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.8681474924087524</v>
+        <v>0.8681475</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9994595646858215</v>
+        <v>0.99945956</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.7938547134399414</v>
+        <v>0.7938547</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.8756176233291626</v>
+        <v>0.8756176</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.7619529962539673</v>
+        <v>0.761953</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.984997749328613</v>
+        <v>-4.9849977</v>
       </c>
       <c r="AV19" s="3">
-        <v>94.06256103515625</v>
+        <v>94.06256</v>
       </c>
       <c r="AW19" s="3">
-        <v>10.70411396026611</v>
+        <v>10.704114</v>
       </c>
       <c r="AX19" s="3">
         <v>420.5320000000001</v>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>28.10703659057617</v>
+        <v>28.107037</v>
       </c>
       <c r="AB20" s="3">
-        <v>28.69431114196777</v>
+        <v>28.694311</v>
       </c>
       <c r="AC20" s="3">
-        <v>48.72861862182617</v>
+        <v>48.72862</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -4885,55 +4885,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.1811548173427582</v>
+        <v>0.18115482</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.6515179872512817</v>
+        <v>0.651518</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.6622465252876282</v>
+        <v>0.6622465</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.09961003810167313</v>
+        <v>0.09961004</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.9535791277885437</v>
+        <v>0.9535791</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.1615897864103317</v>
+        <v>0.16158979</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.2876680791378021</v>
+        <v>0.28766808</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.4636885225772858</v>
+        <v>0.46368852</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.4422608017921448</v>
+        <v>0.4422608</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.9085427522659302</v>
+        <v>0.90854275</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9986909627914429</v>
+        <v>0.99869096</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.7246156930923462</v>
+        <v>0.7246157</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.8257194757461548</v>
+        <v>0.8257195000000001</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.8465056419372559</v>
+        <v>0.8465056399999999</v>
       </c>
       <c r="AU20" s="3">
-        <v>-5.251671314239502</v>
+        <v>-5.2516713</v>
       </c>
       <c r="AV20" s="3">
-        <v>95.00550842285156</v>
+        <v>95.00551</v>
       </c>
       <c r="AW20" s="3">
-        <v>11.14853286743164</v>
+        <v>11.148533</v>
       </c>
       <c r="AX20" s="3">
         <v>431.5840000000002</v>
@@ -4942,7 +4942,7 @@
         <v>3.406800000000001</v>
       </c>
       <c r="AZ20" s="3">
-        <v>0.3984526300599843</v>
+        <v>0.3984526300599842</v>
       </c>
       <c r="BA20" s="3">
         <v>4</v>
@@ -5019,7 +5019,7 @@
         <v>0.5417904351222217</v>
       </c>
       <c r="R21" s="3">
-        <v>1.974734185099057</v>
+        <v>1.974734185099056</v>
       </c>
       <c r="S21" s="3">
         <v>262.6196088127128</v>
@@ -5048,13 +5048,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>22.30717849731445</v>
+        <v>22.307178</v>
       </c>
       <c r="AB21" s="3">
-        <v>20.03717041015625</v>
+        <v>20.03717</v>
       </c>
       <c r="AC21" s="3">
-        <v>52.28086471557617</v>
+        <v>52.280865</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -5066,55 +5066,55 @@
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.1634544134140015</v>
+        <v>0.16345441</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.69719398021698</v>
+        <v>0.697194</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.6966174840927124</v>
+        <v>0.6966175</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.08969704806804657</v>
+        <v>0.08969705</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.9630613327026367</v>
+        <v>0.96306133</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.2257703840732574</v>
+        <v>0.22577038</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.3366061151027679</v>
+        <v>0.33660612</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.5271130800247192</v>
+        <v>0.5271131</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.4627062678337097</v>
+        <v>0.46270627</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.9494125247001648</v>
+        <v>0.9494125</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9993936419487</v>
+        <v>0.99939364</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.7522884607315063</v>
+        <v>0.75228846</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.8586667776107788</v>
+        <v>0.8586668</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.8462157249450684</v>
+        <v>0.8462157</v>
       </c>
       <c r="AU21" s="3">
-        <v>-5.302098274230957</v>
+        <v>-5.3020983</v>
       </c>
       <c r="AV21" s="3">
-        <v>92.66982269287109</v>
+        <v>92.66982</v>
       </c>
       <c r="AW21" s="3">
-        <v>12.74984073638916</v>
+        <v>12.749841</v>
       </c>
       <c r="AX21" s="3">
         <v>431.5840000000002</v>
@@ -5188,7 +5188,7 @@
         <v>0.5470367383247328</v>
       </c>
       <c r="N22" s="3">
-        <v>51.24377626532831</v>
+        <v>51.24377626532832</v>
       </c>
       <c r="O22" s="3">
         <v>74.71041793425144</v>
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>31.98368453979492</v>
+        <v>31.983685</v>
       </c>
       <c r="AB22" s="3">
-        <v>31.56573486328125</v>
+        <v>31.565735</v>
       </c>
       <c r="AC22" s="3">
-        <v>51.06867218017578</v>
+        <v>51.068672</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -5247,55 +5247,55 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.1960595548152924</v>
+        <v>0.19605955</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.6519122719764709</v>
+        <v>0.6519123</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.636513352394104</v>
+        <v>0.63651335</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.1000093072652817</v>
+        <v>0.10000931</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.9555538296699524</v>
+        <v>0.9555538</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.2145793437957764</v>
+        <v>0.21457934</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.2550626397132874</v>
+        <v>0.25506264</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.3734226822853088</v>
+        <v>0.37342268</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.4869077205657959</v>
+        <v>0.48690772</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.8911203145980835</v>
+        <v>0.8911203</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9990541338920593</v>
+        <v>0.99905413</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.7657650113105774</v>
+        <v>0.765765</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.8602112531661987</v>
+        <v>0.86021125</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.8396522402763367</v>
+        <v>0.83965224</v>
       </c>
       <c r="AU22" s="3">
-        <v>-5.287175178527832</v>
+        <v>-5.287175</v>
       </c>
       <c r="AV22" s="3">
-        <v>93.91284942626953</v>
+        <v>93.91285000000001</v>
       </c>
       <c r="AW22" s="3">
-        <v>12.82140350341797</v>
+        <v>12.8214035</v>
       </c>
       <c r="AX22" s="3">
         <v>431.5840000000002</v>
